--- a/saidas/ordens_dia/ordem_dia_2026_08_28_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_08_28_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE5"/>
+  <dimension ref="A1:DE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>VETADA — esperança histórica insuficiente</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1007,109 +1007,113 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3459</v>
+        <v>0.1482</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5376</v>
+        <v>0.2267</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3052</v>
+        <v>0.4201</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8646</v>
+        <v>-0.1615</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2576</v>
+        <v>-0.0142</v>
       </c>
       <c r="R2" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5613</v>
+        <v>-0.0142</v>
       </c>
       <c r="T2" t="n">
-        <v>269</v>
+        <v>322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6624</v>
+        <v>-0.0311</v>
       </c>
       <c r="V2" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0343</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
       <c r="Z2" t="n">
-        <v>0.7845</v>
+        <v>-0.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4515</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6614</v>
+        <v>-0.0321</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7845</v>
+        <v>0.008</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1429</v>
+        <v>0.0045</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.156</v>
+        <v>0.0245</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2632</v>
+        <v>0.028</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0144</v>
+        <v>0.0117</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.4415</v>
+        <v>0.2698</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.11</v>
+        <v>18.92</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81.75</v>
+        <v>19.43</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.2291</v>
+        <v>-0.0046</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.099329</v>
+        <v>0.055746</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.054078</v>
+        <v>1.121181</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.41</v>
+        <v>12.12</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1118,19 +1122,19 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.114031</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.08</v>
+        <v>1.116819</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.97</v>
+        <v>0.873772</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
@@ -1139,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.040095</v>
+        <v>0.032563</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.4774</v>
+        <v>1.7119</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1157,28 +1161,24 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI2" t="n">
@@ -1200,78 +1200,78 @@
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BP2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.505050505050505</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="BR2" t="n">
         <v>1</v>
       </c>
       <c r="BS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.6555</v>
+        <v>0.647</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.6412</v>
+        <v>0.6573</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.4975</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.4369162419749876</v>
+        <v>0.3779308827479717</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.6048227850485501</v>
+        <v>0.6219595510964607</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.4615830351918633</v>
+        <v>0.1817909218890814</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.6048227850485501</v>
+        <v>0.6219595510964607</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.4906542056074766</v>
+        <v>0.5503875968992248</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.7342657342657343</v>
+        <v>0.5546875</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.5488721804511278</v>
+        <v>0.6408450704225352</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.8156424581005587</v>
+        <v>0.5481927710843374</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.515625</v>
+        <v>0</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.2088607594936709</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1281,83 +1281,51 @@
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="CP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.6017</v>
+        <v>0.5799</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.6017</v>
+        <v>0.5799</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.661 | spread_35_20: esp=+0.143 | spread_45_25: esp=+0.156 | spread_45_15: esp=+0.263</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.784 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>vetada</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1366,83 +1334,83 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Monitorar CALL (VETADA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>VETADA — esperança histórica insuficiente</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Monitorar CALL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>monitorar_e6_quase_nivel_a</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0839</v>
+        <v>0.0626</v>
       </c>
       <c r="M3" t="n">
-        <v>0.525</v>
+        <v>0.6667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2642</v>
+        <v>0.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5604</v>
+        <v>0.446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1488</v>
+        <v>0.126</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1423</v>
+        <v>0.0226</v>
       </c>
       <c r="R3" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0348</v>
+        <v>0.1206</v>
       </c>
       <c r="T3" t="n">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0864</v>
+        <v>0.0152</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0585</v>
+        <v>0.0623</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1450,84 +1418,88 @@
           <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
       <c r="Z3" t="n">
-        <v>0.1319</v>
+        <v>-0.18</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0854</v>
+        <v>0.0142</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1319</v>
+        <v>0.0553</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0477</v>
+        <v>0.0313</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0494</v>
+        <v>0.0358</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0537</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0243</v>
+        <v>0.0136</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2705</v>
+        <v>0.2803</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.33</v>
+        <v>28.71</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7.86</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0072</v>
+        <v>0.001</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.056147</v>
+        <v>0.038179</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.334733</v>
+        <v>1.079039</v>
       </c>
       <c r="AN3" t="n">
-        <v>33.47</v>
+        <v>7.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.265989</v>
+        <v>1.092646</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.265989</v>
+        <v>1.111283</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.933225</v>
       </c>
       <c r="AV3" t="n">
         <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.06793100000000001</v>
+        <v>0.037934</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.8265</v>
+        <v>1.0065</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1542,24 +1514,28 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI3" t="n">
@@ -1572,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
@@ -1581,78 +1557,78 @@
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="BP3" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.9595959595959596</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS3" t="n">
         <v>1</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>exec_baixa</t>
+          <t>exec_bilateral</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>exec_expansion_alerta_gap</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.5255</v>
+        <v>0.6855</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.6192</v>
+        <v>0.604</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.4521</v>
+        <v>0.5331</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.33232068066348</v>
+        <v>0.4500888526862044</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.4749588017428233</v>
+        <v>0.6043632288353558</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7186358728261575</v>
+        <v>0.5321149388232496</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.7186358728261575</v>
+        <v>0.6043632288353558</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.8</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1449275362318841</v>
+        <v>0.183206106870229</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.1616161616161616</v>
+        <v>0.3218390804597701</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.1592356687898089</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>aprovado_alerta_gap_generalizacao</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1675,780 +1651,38 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4639</v>
+        <v>0.5395</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.4639</v>
+        <v>0.2698</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.085 | spread_35_20: esp=+0.048 | spread_45_25: esp=+0.049 | spread_45_15: esp=+0.086</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.132 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Monitorar CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>monitorar_e6_quase_nivel_a</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>70</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1464</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7857</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.2297</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.4201</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.1578</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="R4" t="n">
-        <v>458</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="T4" t="n">
-        <v>321</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.0292</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.0348</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.0302</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.3062</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>18.79</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.0043</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.06398</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.109768</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.114031</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.116819</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.873772</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.03397</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.8834</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>neutro_zona_cinza</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>37</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>exec_alta</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>exec_expansion_har</t>
-        </is>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.6573</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.4975</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.3779308827479717</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.6219595510964607</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.1817909218890814</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0.6219595510964607</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0.5503875968992248</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0.5546875</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0.6408450704225352</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0.5481927710843374</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>har_fallback_aprovado_expansao</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="CN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>0.5897</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>0.2948</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
           <t>vetada</t>
         </is>
       </c>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EGIE3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Monitorar CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>monitorar_e6_quase_nivel_a</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0629</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.0281</v>
-      </c>
-      <c r="R5" t="n">
-        <v>457</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1206</v>
-      </c>
-      <c r="T5" t="n">
-        <v>353</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0623</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.0358</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.3443</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.041307</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.056579</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.092646</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.111283</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.933225</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.04069</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.0151</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>neutro_zona_cinza</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>52</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.4848484848484849</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>exec_bilateral</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>exec_expansion_alerta_gap</t>
-        </is>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.6855</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.5331</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.4500888526862044</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.6043632288353558</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.5321149388232496</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0.6043632288353558</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0.183206106870229</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0.7567567567567568</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0.3218390804597701</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.6756756756756757</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0.1592356687898089</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>aprovado_alerta_gap_generalizacao</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>0.5276</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>0.2638</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2576,41 +1810,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>0.66</v>
       </c>
       <c r="I2" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="J2" t="n">
-        <v>-48.48</v>
+        <v>-36.36</v>
       </c>
       <c r="K2" t="n">
-        <v>1.791</v>
+        <v>1.26</v>
       </c>
       <c r="L2" t="n">
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.301</v>
+        <v>0.77</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.07</v>
+        <v>0.929</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4412</v>
+        <v>-0.278</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M=1.79 ≥ BE+alvo=0.79 | lucro≈+1.30DP</t>
+          <t>M=1.26 ≥ BE+alvo=0.79 | lucro≈+0.77DP</t>
         </is>
       </c>
     </row>
@@ -2639,7 +1873,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -2648,52 +1882,52 @@
         <v>5.19</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="J3" t="n">
-        <v>-13.23</v>
+        <v>-14.39</v>
       </c>
       <c r="K3" t="n">
-        <v>1.241</v>
+        <v>1.412</v>
       </c>
       <c r="L3" t="n">
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.751</v>
+        <v>0.922</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.273</v>
+        <v>0.205</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0218</v>
+        <v>0.0153</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>M=1.24 ≥ BE+alvo=0.79 | lucro≈+0.75DP</t>
+          <t>M=1.41 ≥ BE+alvo=0.79 | lucro≈+0.92DP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRAP4</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SINAL INVERTIDO</t>
+          <t>ENCERRAR (vencimento)</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2702,22 +1936,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>20.25</v>
+        <v>26.05</v>
       </c>
       <c r="I4" t="n">
-        <v>22.35</v>
+        <v>23.75</v>
       </c>
       <c r="J4" t="n">
-        <v>10.37</v>
+        <v>-8.82</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.24</v>
+        <v>-0.904</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
@@ -2726,24 +1960,24 @@
         <v>-0.32</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.898</v>
+        <v>0.456</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0843</v>
+        <v>-0.031</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Modelo virou CALL | M=-1.24 | razao=1.90</t>
+          <t>3d restantes — theta domina | M=-0.90 | lucro≈-0.32DP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>BRAP4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2752,7 +1986,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2765,22 +1999,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>7.44</v>
+        <v>20.25</v>
       </c>
       <c r="I5" t="n">
-        <v>8.859999999999999</v>
+        <v>21.88</v>
       </c>
       <c r="J5" t="n">
-        <v>19.09</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.759</v>
+        <v>-0.822</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
@@ -2792,34 +2026,34 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.85</v>
+        <v>0.983</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1007</v>
+        <v>0.0476</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Modelo virou CALL | M=-0.76 | razao=0.85</t>
+          <t>Modelo virou CALL | M=-0.82 | razao=0.98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GGBR4</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>SINAL INVERTIDO</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2828,22 +2062,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>26.05</v>
+        <v>7.44</v>
       </c>
       <c r="I6" t="n">
-        <v>23.97</v>
+        <v>8.85</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.97</v>
+        <v>18.95</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.803</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>0.49</v>
@@ -2852,24 +2086,24 @@
         <v>-0.32</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0117</v>
+        <v>0.1125</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.17 &lt; 0.6 | M=-0.80 — ativo foi contra, tese falhou</t>
+          <t>Modelo virou CALL | M=-0.81 | razao=1.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2878,7 +2112,7 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46259</v>
+        <v>46248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2887,52 +2121,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>9.84</v>
+        <v>3.91</v>
       </c>
       <c r="I7" t="n">
-        <v>10.45</v>
+        <v>4.57</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>16.88</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.356</v>
+        <v>-0.527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.255</v>
+        <v>-0.32</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.574</v>
+        <v>0.051</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0396</v>
+        <v>0.0068</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>razao=0.57 &lt; 0.6 | M=-0.36 — ativo foi contra, tese falhou</t>
+          <t>razao=0.05 &lt; 0.6 | M=-0.53 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2941,7 +2175,7 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2954,22 +2188,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>3.91</v>
+        <v>46.57</v>
       </c>
       <c r="I8" t="n">
-        <v>4.84</v>
+        <v>48.61</v>
       </c>
       <c r="J8" t="n">
-        <v>23.79</v>
+        <v>4.38</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.883</v>
+        <v>-0.405</v>
       </c>
       <c r="L8" t="n">
         <v>0.49</v>
@@ -2981,30 +2215,30 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.422</v>
+        <v>0.376</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0549</v>
+        <v>-0.0165</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>razao=0.42 &lt; 0.6 | M=-0.88 — ativo foi contra, tese falhou</t>
+          <t>razao=0.38 &lt; 0.6 | M=-0.40 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3017,22 +2251,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>46.57</v>
+        <v>16.78</v>
       </c>
       <c r="I9" t="n">
-        <v>48.34</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>1.31</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.305</v>
+        <v>0.032</v>
       </c>
       <c r="L9" t="n">
         <v>0.49</v>
@@ -3044,21 +2278,21 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.425</v>
+        <v>0.03</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0194</v>
+        <v>-0.0013</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>razao=0.42 &lt; 0.6 | M=-0.31 — ativo foi contra, tese falhou</t>
+          <t>razao=0.03 &lt; 0.6 | M=0.03 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3067,7 +2301,7 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3080,41 +2314,41 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>16.78</v>
+        <v>8.33</v>
       </c>
       <c r="I10" t="n">
-        <v>16.93</v>
+        <v>8.34</v>
       </c>
       <c r="J10" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="K10" t="n">
-        <v>0.096</v>
+        <v>0.193</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32</v>
+        <v>-0.297</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.223</v>
+        <v>0.393</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0251</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>razao=0.22 &lt; 0.6 | M=0.10 — movimento OK, modelo ruidoso</t>
+          <t>razao=0.39 &lt; 0.6 | M=0.19 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
@@ -3143,22 +2377,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
         <v>14.57</v>
       </c>
       <c r="I11" t="n">
-        <v>14.57</v>
+        <v>14.53</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.154</v>
+        <v>-0.227</v>
       </c>
       <c r="L11" t="n">
         <v>0.425</v>
@@ -3170,21 +2404,21 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.758</v>
+        <v>0.664</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0321</v>
+        <v>0.0241</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=-0.15 | razao=0.76 | 0/20d</t>
+          <t>M=-0.23 | razao=0.66 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3193,7 +2427,7 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3202,45 +2436,45 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>8.33</v>
+        <v>9.84</v>
       </c>
       <c r="I12" t="n">
-        <v>8.33</v>
+        <v>10.33</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="K12" t="n">
-        <v>0.205</v>
+        <v>-0.253</v>
       </c>
       <c r="L12" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.285</v>
+        <v>-0.255</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.827</v>
+        <v>0.781</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0561</v>
+        <v>-0.053</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.20 | razao=0.83 | 0/20d</t>
+          <t>M=-0.25 | razao=0.78 | 3/20d</t>
         </is>
       </c>
     </row>
@@ -3269,22 +2503,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
         <v>79.11</v>
       </c>
       <c r="I13" t="n">
-        <v>79.11</v>
+        <v>77.84</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.162</v>
+        <v>-0.385</v>
       </c>
       <c r="L13" t="n">
         <v>0.49</v>
@@ -3296,14 +2530,14 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.477</v>
+        <v>1.633</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0993</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=-0.16 | razao=2.48 | 0/20d</t>
+          <t>M=-0.38 | razao=1.63 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -3332,37 +2566,37 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
         <v>4.11</v>
       </c>
       <c r="I14" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="J14" t="n">
-        <v>2.68</v>
+        <v>3.89</v>
       </c>
       <c r="K14" t="n">
-        <v>0.352</v>
+        <v>0.301</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.138</v>
+        <v>-0.189</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.907</v>
+        <v>0.844</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2226</v>
+        <v>-0.1986</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3381,7 +2615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3494,19 +2728,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4415</v>
+        <v>0.2698</v>
       </c>
       <c r="D2" t="n">
-        <v>1.054078</v>
+        <v>1.121181</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3514,71 +2748,39 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.6624</v>
+        <v>-0.0311</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>vetada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.784 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0144</v>
+        <v>0.0117</v>
       </c>
       <c r="S2" t="n">
-        <v>22.9</v>
+        <v>18.6</v>
       </c>
       <c r="T2" t="n">
-        <v>24.1</v>
+        <v>20.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3589,19 +2791,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Monitorar CALL (VETADA)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2705</v>
+        <v>0.2803</v>
       </c>
       <c r="D3" t="n">
-        <v>1.334733</v>
+        <v>1.079039</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3609,199 +2811,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.0864</v>
+        <v>0.0152</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>vetada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.132 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0243</v>
+        <v>0.0136</v>
       </c>
       <c r="S3" t="n">
-        <v>38.6</v>
+        <v>21.6</v>
       </c>
       <c r="T3" t="n">
-        <v>51.5</v>
+        <v>23.3</v>
       </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Monitorar CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.3062</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.109768</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.0292</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="S4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EGIE3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Monitorar CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3443</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.056579</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="S5" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -4365,7 +3409,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4398,7 +3442,7 @@
         <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0482</v>
+        <v>0.0483</v>
       </c>
       <c r="L2" t="n">
         <v>0.6957</v>
@@ -4463,13 +3507,13 @@
         <v>0.0856</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0106</v>
+        <v>0.0111</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4045</v>
+        <v>0.4399</v>
       </c>
       <c r="AH2" t="n">
-        <v>172.4</v>
+        <v>171.82</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4478,13 +3522,13 @@
         <v>0.0208</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.04102</v>
+        <v>0.04179</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.945458</v>
+        <v>0.943898</v>
       </c>
       <c r="AM2" t="n">
-        <v>-5.45</v>
+        <v>-5.61</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4514,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.029626</v>
+        <v>0.030976</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.3846</v>
+        <v>1.3491</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4669,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5399</v>
+        <v>0.5293</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -4698,7 +3742,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4731,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0461</v>
+        <v>0.0459</v>
       </c>
       <c r="L3" t="n">
         <v>0.5455</v>
@@ -4746,16 +3790,16 @@
         <v>-0.1257</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0431</v>
+        <v>-0.0407</v>
       </c>
       <c r="Q3" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R3" t="n">
         <v>-0.0404</v>
       </c>
       <c r="S3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0576</v>
@@ -4800,28 +3844,28 @@
         <v>-0.0392</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.017</v>
+        <v>0.0171</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4408</v>
+        <v>0.445</v>
       </c>
       <c r="AH3" t="n">
-        <v>42.7</v>
+        <v>43.36</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0027</v>
+        <v>-0.0026</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.023124</v>
+        <v>0.026614</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.945589</v>
+        <v>0.9609220000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>-5.44</v>
+        <v>-3.91</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -4851,10 +3895,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.047443</v>
+        <v>0.047673</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4874</v>
+        <v>0.5583</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -5002,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.4687</v>
+        <v>0.4749</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -5031,7 +4075,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5040,7 +4084,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5049,32 +4093,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3459</v>
+        <v>0.3445</v>
       </c>
       <c r="L4" t="n">
         <v>0.7272999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5376</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>1.3052</v>
@@ -5083,22 +4123,22 @@
         <v>0.8646</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2576</v>
+        <v>0.2349</v>
       </c>
       <c r="Q4" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5613</v>
+        <v>0.5607</v>
       </c>
       <c r="S4" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T4" t="n">
         <v>0.6624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -5133,34 +4173,34 @@
         <v>0.2632</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0144</v>
+        <v>0.0154</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4415</v>
+        <v>0.4918</v>
       </c>
       <c r="AH4" t="n">
-        <v>79.11</v>
+        <v>77.84</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.75</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2291</v>
+        <v>0.2282</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.099329</v>
+        <v>0.06998699999999999</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.054078</v>
+        <v>1.014308</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.41</v>
+        <v>1.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -5181,13 +4221,13 @@
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.040095</v>
+        <v>0.042866</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.4774</v>
+        <v>1.6327</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -5339,71 +4379,27 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.6017</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.6017</v>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>Call delta~50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>Call delta~40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>OTM extremo (&lt;delta~20) sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.661 | spread_35_20: esp=+0.143 | spread_45_25: esp=+0.156 | spread_45_15: esp=+0.263</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.784 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5412,7 +4408,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5445,13 +4441,13 @@
         <v>177</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3711</v>
+        <v>0.3695</v>
       </c>
       <c r="L5" t="n">
         <v>0.6667</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3421</v>
+        <v>0.3403</v>
       </c>
       <c r="N5" t="n">
         <v>0.8602</v>
@@ -5460,22 +4456,22 @@
         <v>0.0985</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1023</v>
+        <v>0.1072</v>
       </c>
       <c r="Q5" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1298</v>
+        <v>0.1307</v>
       </c>
       <c r="S5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="T5" t="n">
         <v>0.207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.048</v>
+        <v>0.0479</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -5510,28 +4506,28 @@
         <v>0.1227</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0169</v>
+        <v>0.0157</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5405</v>
+        <v>0.4519</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.93</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0765</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.010481</v>
+        <v>-0.001302</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.197488</v>
+        <v>1.140773</v>
       </c>
       <c r="AM5" t="n">
-        <v>19.75</v>
+        <v>14.08</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
@@ -5561,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.047068</v>
+        <v>0.043817</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2227</v>
+        <v>0.0297</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -5716,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.3783</v>
+        <v>0.3767</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -5745,7 +4741,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5778,7 +4774,7 @@
         <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0629</v>
+        <v>0.063</v>
       </c>
       <c r="L6" t="n">
         <v>0.4</v>
@@ -5847,13 +4843,13 @@
         <v>-0.1094</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0137</v>
+        <v>0.0144</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2788</v>
+        <v>0.3241</v>
       </c>
       <c r="AH6" t="n">
-        <v>105.17</v>
+        <v>104.8</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -5862,13 +4858,13 @@
         <v>-0.0056</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.014279</v>
+        <v>0.012392</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.12178</v>
+        <v>1.126943</v>
       </c>
       <c r="AM6" t="n">
-        <v>12.18</v>
+        <v>12.69</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -5898,10 +4894,10 @@
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.038368</v>
+        <v>0.040112</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3721</v>
+        <v>0.3089</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -6053,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.4827</v>
+        <v>0.4673</v>
       </c>
       <c r="CQ6" t="n">
         <v>0</v>
@@ -6082,7 +5078,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6108,20 +5104,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>65</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1363</v>
+        <v>0.1357</v>
       </c>
       <c r="L7" t="n">
         <v>0.3231</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1538</v>
+        <v>0.1515</v>
       </c>
       <c r="N7" t="n">
         <v>0.5449000000000001</v>
@@ -6133,19 +5129,19 @@
         <v>0.023</v>
       </c>
       <c r="Q7" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R7" t="n">
         <v>0.0448</v>
       </c>
       <c r="S7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="T7" t="n">
         <v>-0.06469999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0365</v>
+        <v>0.0362</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -6184,13 +5180,13 @@
         <v>-0.08260000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0223</v>
+        <v>0.0206</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.4132</v>
+        <v>0.3422</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.73</v>
+        <v>15.91</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -6199,13 +5195,13 @@
         <v>-0.008800000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.038848</v>
+        <v>0.050551</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.026994</v>
+        <v>1.029079</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -6235,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.062345</v>
+        <v>0.057348</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.6231</v>
+        <v>0.8815</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -6248,7 +5244,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -6390,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4343</v>
+        <v>0.4744</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -6419,7 +5415,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6452,13 +5448,13 @@
         <v>96</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2013</v>
+        <v>0.2004</v>
       </c>
       <c r="L8" t="n">
         <v>0.5104</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3711</v>
+        <v>0.3636</v>
       </c>
       <c r="N8" t="n">
         <v>1.0826</v>
@@ -6470,19 +5466,19 @@
         <v>-0.057</v>
       </c>
       <c r="Q8" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R8" t="n">
         <v>-0.0044</v>
       </c>
       <c r="S8" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T8" t="n">
         <v>0.2909</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6521,28 +5517,28 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0466</v>
+        <v>0.0478</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.8746</v>
+        <v>0.9488</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.84</v>
+        <v>4.57</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0585</v>
+        <v>0.0583</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.054922</v>
+        <v>0.006846</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.017724</v>
+        <v>1.015978</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -6572,10 +5568,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.130029</v>
+        <v>0.133418</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.4224</v>
+        <v>0.0513</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -6727,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.3709</v>
+        <v>0.319</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -6756,7 +5752,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6789,13 +5785,13 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2096</v>
+        <v>0.2088</v>
       </c>
       <c r="L9" t="n">
         <v>0.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1881</v>
+        <v>0.19</v>
       </c>
       <c r="N9" t="n">
         <v>0.9039</v>
@@ -6804,22 +5800,22 @@
         <v>0.1074</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0813</v>
+        <v>-0.0854</v>
       </c>
       <c r="Q9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.0545</v>
+        <v>-0.0549</v>
       </c>
       <c r="S9" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="T9" t="n">
         <v>0.0331</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0529</v>
+        <v>0.0531</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -6858,13 +5854,13 @@
         <v>-0.0372</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0183</v>
+        <v>0.0182</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4169</v>
+        <v>0.4115</v>
       </c>
       <c r="AH9" t="n">
-        <v>47.31</v>
+        <v>47.94</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -6873,13 +5869,13 @@
         <v>0.0069</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004492</v>
+        <v>0.004921</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.101302</v>
+        <v>1.059267</v>
       </c>
       <c r="AM9" t="n">
-        <v>10.13</v>
+        <v>5.93</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -6909,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.050986</v>
+        <v>0.05066</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0881</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -7064,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.4154</v>
+        <v>0.4174</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -7093,7 +6089,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7126,7 +6122,7 @@
         <v>69</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1447</v>
+        <v>0.1441</v>
       </c>
       <c r="L10" t="n">
         <v>0.7681</v>
@@ -7141,16 +6137,16 @@
         <v>0.5461</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1344</v>
+        <v>0.1566</v>
       </c>
       <c r="Q10" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1566</v>
+        <v>0.1578</v>
       </c>
       <c r="S10" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T10" t="n">
         <v>0.3308</v>
@@ -7195,28 +6191,28 @@
         <v>0.3263</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0193</v>
+        <v>0.0183</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3273</v>
+        <v>0.2962</v>
       </c>
       <c r="AH10" t="n">
-        <v>46.4</v>
+        <v>46.15</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0479</v>
+        <v>0.0477</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.086439</v>
+        <v>0.08000599999999999</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.997126</v>
+        <v>1.018475</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.29</v>
+        <v>1.85</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -7246,10 +6242,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.053967</v>
+        <v>0.051166</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.6017</v>
+        <v>1.5637</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -7397,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.5309</v>
+        <v>0.5334</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -7426,7 +6422,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7459,7 +6455,7 @@
         <v>126</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2642</v>
+        <v>0.263</v>
       </c>
       <c r="L11" t="n">
         <v>0.6746</v>
@@ -7474,16 +6470,16 @@
         <v>0.4588</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1549</v>
+        <v>0.1569</v>
       </c>
       <c r="Q11" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R11" t="n">
-        <v>0.249</v>
+        <v>0.2525</v>
       </c>
       <c r="S11" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="T11" t="n">
         <v>0.2409</v>
@@ -7528,28 +6524,28 @@
         <v>0.1691</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0251</v>
+        <v>0.0244</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.9466</v>
+        <v>0.9029</v>
       </c>
       <c r="AH11" t="n">
-        <v>23.97</v>
+        <v>23.75</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0636</v>
+        <v>0.0634</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.011664</v>
+        <v>-0.030993</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.8776659999999999</v>
+        <v>0.805027</v>
       </c>
       <c r="AM11" t="n">
-        <v>-12.23</v>
+        <v>-19.5</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -7579,10 +6575,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.069926</v>
+        <v>0.068026</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1668</v>
+        <v>0.4556</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -7734,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.2874</v>
+        <v>0.325</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -7763,7 +6759,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7796,7 +6792,7 @@
         <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0668</v>
       </c>
       <c r="L12" t="n">
         <v>0.6562</v>
@@ -7805,52 +6801,48 @@
         <v>0.3438</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>0.8801</v>
       </c>
       <c r="O12" t="n">
         <v>0.1056</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1484</v>
+        <v>-0.1454</v>
       </c>
       <c r="Q12" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.0895</v>
+        <v>-0.089</v>
       </c>
       <c r="S12" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1998</v>
+        <v>0.1999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1049</v>
+        <v>0.1048</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>risco</t>
-        </is>
-      </c>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.1485</v>
+        <v>0.2882</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5818</v>
+        <v>0.9008</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1988</v>
+        <v>0.1989</v>
       </c>
       <c r="AB12" t="n">
         <v>0.2882</v>
@@ -7865,13 +6857,13 @@
         <v>0.1485</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0284</v>
+        <v>0.0267</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.64</v>
+        <v>0.5557</v>
       </c>
       <c r="AH12" t="n">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -7880,13 +6872,13 @@
         <v>0.0134</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.083123</v>
+        <v>-0.081173</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.938676</v>
+        <v>1.026378</v>
       </c>
       <c r="AM12" t="n">
-        <v>-6.13</v>
+        <v>2.64</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -7898,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>1.03</v>
@@ -7916,10 +6908,10 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.07921</v>
+        <v>0.074438</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.0494</v>
+        <v>1.0905</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -7934,7 +6926,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC12" t="n">
@@ -8067,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.4556</v>
+        <v>0.4765</v>
       </c>
       <c r="CQ12" t="n">
         <v>0</v>
@@ -8096,7 +7088,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -8122,14 +7114,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>47</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0985</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>0.617</v>
@@ -8147,7 +7139,7 @@
         <v>0.0253</v>
       </c>
       <c r="Q13" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R13" t="n">
         <v>0.065</v>
@@ -8194,13 +7186,13 @@
         <v>0.0824</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0143</v>
+        <v>0.0136</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5762</v>
+        <v>0.5288</v>
       </c>
       <c r="AH13" t="n">
-        <v>39.45</v>
+        <v>40.02</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -8209,13 +7201,13 @@
         <v>0.0014</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.027043</v>
+        <v>0.030878</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.865275</v>
+        <v>0.945589</v>
       </c>
       <c r="AM13" t="n">
-        <v>-13.47</v>
+        <v>-5.44</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -8227,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>1.125259</v>
@@ -8245,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.039805</v>
+        <v>0.038046</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.6794</v>
+        <v>0.8116</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -8258,7 +7250,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -8396,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.3302</v>
+        <v>0.3529</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -8425,7 +7417,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -8451,20 +7443,20 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>73</v>
       </c>
       <c r="K14" t="n">
-        <v>0.153</v>
+        <v>0.1524</v>
       </c>
       <c r="L14" t="n">
         <v>0.3151</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1507</v>
+        <v>0.1486</v>
       </c>
       <c r="N14" t="n">
         <v>0.3312</v>
@@ -8473,22 +7465,22 @@
         <v>-0.0471</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0833</v>
+        <v>0.0844</v>
       </c>
       <c r="Q14" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1222</v>
+        <v>0.1163</v>
       </c>
       <c r="S14" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="T14" t="n">
         <v>-0.094</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0271</v>
+        <v>0.0269</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8497,7 +7489,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -8527,28 +7519,28 @@
         <v>-0.0764</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0366</v>
+        <v>0.0392</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5558</v>
+        <v>0.6681</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.47</v>
+        <v>5.17</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.0144</v>
+        <v>-0.0143</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.130763</v>
+        <v>0.086636</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.8904570000000001</v>
+        <v>0.866666</v>
       </c>
       <c r="AM14" t="n">
-        <v>-10.95</v>
+        <v>-13.33</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -8578,10 +7570,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.102084</v>
+        <v>0.109355</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.2809</v>
+        <v>0.7922</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -8591,7 +7583,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -8733,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.5153</v>
+        <v>0.444</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -8762,7 +7754,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -8795,7 +7787,7 @@
         <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0356</v>
+        <v>0.0355</v>
       </c>
       <c r="L15" t="n">
         <v>0.4118</v>
@@ -8813,13 +7805,13 @@
         <v>-0.1208</v>
       </c>
       <c r="Q15" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R15" t="n">
         <v>0.08890000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T15" t="n">
         <v>0.1308</v>
@@ -8864,28 +7856,28 @@
         <v>-0.0496</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0098</v>
+        <v>0.0094</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0019</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>15.12</v>
+        <v>15.07</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0047</v>
+        <v>0.0046</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.003669</v>
+        <v>-0.010584</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.29645</v>
+        <v>1.283486</v>
       </c>
       <c r="AM15" t="n">
-        <v>29.64</v>
+        <v>28.35</v>
       </c>
       <c r="AN15" t="n">
         <v>1</v>
@@ -8915,10 +7907,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.027482</v>
+        <v>0.026341</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1335</v>
+        <v>0.4018</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -9070,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.482</v>
+        <v>0.5092</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -9099,7 +8091,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9125,7 +8117,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -9150,7 +8142,7 @@
         <v>-0.0265</v>
       </c>
       <c r="Q16" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R16" t="n">
         <v>-0.1518</v>
@@ -9185,13 +8177,13 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.0411</v>
+        <v>0.0423</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.6561</v>
+        <v>0.6862</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.37</v>
+        <v>5.08</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -9200,13 +8192,13 @@
         <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.128705</v>
+        <v>0.078058</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.853804</v>
+        <v>0.809048</v>
       </c>
       <c r="AM16" t="n">
-        <v>-14.62</v>
+        <v>-19.1</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -9236,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.114819</v>
+        <v>0.118055</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.1209</v>
+        <v>0.6612</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9249,7 +8241,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -9387,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4813</v>
+        <v>0.4293</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -9416,7 +8408,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9449,7 +8441,7 @@
         <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>0.044</v>
+        <v>0.0438</v>
       </c>
       <c r="L17" t="n">
         <v>0.2381</v>
@@ -9458,28 +8450,28 @@
         <v>0.1739</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4516</v>
+        <v>0.6503</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2388</v>
+        <v>0.4944</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1549</v>
+        <v>-0.1512</v>
       </c>
       <c r="Q17" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0065</v>
+        <v>0.0331</v>
       </c>
       <c r="S17" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0596</v>
+        <v>-0.0218</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0593</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9488,7 +8480,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -9503,43 +8495,43 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.0606</v>
+        <v>-0.0228</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.1044</v>
+        <v>-0.0665</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0379</v>
+        <v>-0.0344</v>
       </c>
       <c r="AD17" t="n">
         <v>-0.07190000000000001</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0704</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0298</v>
+        <v>0.0268</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.6397</v>
+        <v>0.517</v>
       </c>
       <c r="AH17" t="n">
-        <v>35.06</v>
+        <v>34.69</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.0026</v>
+        <v>-0.001</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.010571</v>
+        <v>-0.021472</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.040747</v>
+        <v>1.052432</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.07</v>
+        <v>5.24</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -9569,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.083201</v>
+        <v>0.074724</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1271</v>
+        <v>0.2874</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -9720,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.392</v>
+        <v>0.4326</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -9749,7 +8741,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9782,7 +8774,7 @@
         <v>94</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1967</v>
+        <v>0.1962</v>
       </c>
       <c r="L18" t="n">
         <v>0.734</v>
@@ -9797,10 +8789,10 @@
         <v>0.1241</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0516</v>
+        <v>-0.0528</v>
       </c>
       <c r="Q18" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R18" t="n">
         <v>0.2522</v>
@@ -9847,28 +8839,28 @@
         <v>0.1618</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0121</v>
+        <v>0.0116</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4501</v>
+        <v>0.4133</v>
       </c>
       <c r="AH18" t="n">
-        <v>38.7</v>
+        <v>38.67</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1349</v>
+        <v>0.1346</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.035545</v>
+        <v>0.038662</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.960571</v>
+        <v>0.95696</v>
       </c>
       <c r="AM18" t="n">
-        <v>-3.94</v>
+        <v>-4.3</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -9898,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.033883</v>
+        <v>0.032408</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.0491</v>
+        <v>1.193</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -10053,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.4921</v>
+        <v>0.5139</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -10082,7 +9074,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -10108,20 +9100,20 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>40</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0839</v>
+        <v>0.0835</v>
       </c>
       <c r="L19" t="n">
         <v>0.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0.35</v>
+        <v>0.3415</v>
       </c>
       <c r="N19" t="n">
         <v>1.1181</v>
@@ -10133,19 +9125,19 @@
         <v>-0.0151</v>
       </c>
       <c r="Q19" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R19" t="n">
         <v>-0.0442</v>
       </c>
       <c r="S19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T19" t="n">
         <v>0.2812</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1472</v>
+        <v>0.1454</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10180,28 +9172,28 @@
         <v>0.1042</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0252</v>
+        <v>0.0262</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.2897</v>
+        <v>0.3107</v>
       </c>
       <c r="AH19" t="n">
-        <v>23.8</v>
+        <v>22.97</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0236</v>
+        <v>0.0235</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.08823400000000001</v>
+        <v>0.039257</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.9746899999999999</v>
+        <v>0.9741109999999999</v>
       </c>
       <c r="AM19" t="n">
-        <v>-2.53</v>
+        <v>-2.59</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -10231,10 +9223,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.070245</v>
+        <v>0.073184</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.2561</v>
+        <v>0.5364</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -10244,7 +9236,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -10386,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.5406</v>
+        <v>0.4645</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -10415,7 +9407,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -10448,7 +9440,7 @@
         <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0587</v>
+        <v>0.0585</v>
       </c>
       <c r="L20" t="n">
         <v>0.9643</v>
@@ -10463,16 +9455,16 @@
         <v>0.0699</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0693</v>
+        <v>-0.0706</v>
       </c>
       <c r="Q20" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.0205</v>
+        <v>-0.0262</v>
       </c>
       <c r="S20" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="T20" t="n">
         <v>0.4962</v>
@@ -10517,28 +9509,28 @@
         <v>0.1809</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.034</v>
+        <v>0.0305</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.7975</v>
+        <v>0.6582</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.4</v>
+        <v>19.28</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0291</v>
+        <v>0.029</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.04239</v>
+        <v>0.027821</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.685229</v>
+        <v>0.776711</v>
       </c>
       <c r="AM20" t="n">
-        <v>-31.48</v>
+        <v>-22.33</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -10562,16 +9554,16 @@
         <v>0.97</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.094975</v>
+        <v>0.085161</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.4463</v>
+        <v>0.3267</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -10719,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.3506</v>
+        <v>0.3665</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -10748,7 +9740,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -10778,28 +9770,28 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3795</v>
+        <v>0.382</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4365</v>
+        <v>0.4426</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2228</v>
+        <v>0.2312</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5289</v>
+        <v>0.5185</v>
       </c>
       <c r="O21" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="P21" t="n">
         <v>0.0449</v>
       </c>
       <c r="Q21" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R21" t="n">
         <v>0.179</v>
@@ -10808,10 +9800,10 @@
         <v>382</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0147</v>
+        <v>-0.0112</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0259</v>
+        <v>0.0258</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -10835,43 +9827,43 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.0157</v>
+        <v>-0.0122</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.0311</v>
+        <v>-0.0246</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.0134</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.0339</v>
+        <v>-0.0296</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.0318</v>
+        <v>-0.0251</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0233</v>
+        <v>0.0217</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.7866</v>
+        <v>0.7456</v>
       </c>
       <c r="AH21" t="n">
-        <v>25.08</v>
+        <v>25.09</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.0056</v>
+        <v>-0.0043</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.016481</v>
+        <v>0.015232</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.813181</v>
+        <v>0.827363</v>
       </c>
       <c r="AM21" t="n">
-        <v>-18.68</v>
+        <v>-17.26</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -10901,10 +9893,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.064959</v>
+        <v>0.06048</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.2537</v>
+        <v>0.2518</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -11056,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.3506</v>
+        <v>0.3586</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -11085,7 +10077,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -11111,20 +10103,20 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J22" t="n">
         <v>145</v>
       </c>
       <c r="K22" t="n">
-        <v>0.304</v>
+        <v>0.3027</v>
       </c>
       <c r="L22" t="n">
         <v>0.6828</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3226</v>
+        <v>0.3268</v>
       </c>
       <c r="N22" t="n">
         <v>0.7504</v>
@@ -11133,22 +10125,22 @@
         <v>0.2327</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0603</v>
+        <v>0.092</v>
       </c>
       <c r="Q22" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2763</v>
+        <v>0.2822</v>
       </c>
       <c r="S22" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1454</v>
+        <v>0.1463</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0424</v>
+        <v>0.0426</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -11166,49 +10158,49 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>0.0867</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.3398</v>
+        <v>0.3543</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1444</v>
+        <v>0.1453</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1891</v>
+        <v>0.1928</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0444</v>
+        <v>0.0463</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.0457</v>
+        <v>0.0494</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.0867</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0247</v>
+        <v>0.0243</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.955</v>
+        <v>0.9277</v>
       </c>
       <c r="AH22" t="n">
-        <v>10.45</v>
+        <v>10.33</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0442</v>
+        <v>0.0443</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.039565</v>
+        <v>-0.052952</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.840726</v>
+        <v>0.793277</v>
       </c>
       <c r="AM22" t="n">
-        <v>-15.93</v>
+        <v>-20.67</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -11238,10 +10230,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.068879</v>
+        <v>0.067786</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.5744</v>
+        <v>0.7812</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -11251,7 +10243,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -11393,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.3374</v>
+        <v>0.3636</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -11422,7 +10414,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -11459,7 +10451,7 @@
         <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0629</v>
+        <v>0.0626</v>
       </c>
       <c r="L23" t="n">
         <v>0.6667</v>
@@ -11474,10 +10466,10 @@
         <v>0.126</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0281</v>
+        <v>0.0226</v>
       </c>
       <c r="Q23" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R23" t="n">
         <v>0.1206</v>
@@ -11528,13 +10520,13 @@
         <v>0.0537</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0146</v>
+        <v>0.0136</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.3443</v>
+        <v>0.2803</v>
       </c>
       <c r="AH23" t="n">
-        <v>28.85</v>
+        <v>28.71</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -11543,13 +10535,13 @@
         <v>0.001</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.041307</v>
+        <v>0.038179</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.056579</v>
+        <v>1.079039</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.66</v>
+        <v>7.9</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -11579,10 +10571,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.04069</v>
+        <v>0.037934</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.0151</v>
+        <v>1.0065</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -11734,10 +10726,10 @@
         <v>0</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.5276</v>
+        <v>0.5395</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.2638</v>
+        <v>0.2698</v>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
@@ -11775,7 +10767,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -11808,13 +10800,13 @@
         <v>149</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3124</v>
+        <v>0.3111</v>
       </c>
       <c r="L24" t="n">
         <v>0.651</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4172</v>
+        <v>0.42</v>
       </c>
       <c r="N24" t="n">
         <v>1.5678</v>
@@ -11823,22 +10815,22 @@
         <v>1.0091</v>
       </c>
       <c r="P24" t="n">
-        <v>0.058</v>
+        <v>0.0457</v>
       </c>
       <c r="Q24" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4709</v>
+        <v>0.4557</v>
       </c>
       <c r="S24" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="T24" t="n">
         <v>0.5651</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0849</v>
+        <v>0.0852</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -11873,28 +10865,28 @@
         <v>0.1632</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0159</v>
+        <v>0.0174</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.5071</v>
+        <v>0.5794</v>
       </c>
       <c r="AH24" t="n">
-        <v>22.35</v>
+        <v>21.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1765</v>
+        <v>0.1758</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.084313</v>
+        <v>0.047635</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.977142</v>
+        <v>0.922635</v>
       </c>
       <c r="AM24" t="n">
-        <v>-2.29</v>
+        <v>-7.74</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -11906,7 +10898,7 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.044576</v>
@@ -11924,10 +10916,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.04443</v>
+        <v>0.048438</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.8977</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -12079,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.584</v>
+        <v>0.4781</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -12108,7 +11100,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -12141,7 +11133,7 @@
         <v>112</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2343</v>
+        <v>0.2338</v>
       </c>
       <c r="L25" t="n">
         <v>0.5089</v>
@@ -12156,16 +11148,16 @@
         <v>0.2982</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0863</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3708</v>
+        <v>0.3788</v>
       </c>
       <c r="S25" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T25" t="n">
         <v>0.1996</v>
@@ -12210,28 +11202,28 @@
         <v>0.0936</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.9477</v>
+        <v>0.8949</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0468</v>
+        <v>0.0467</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.222612</v>
+        <v>-0.198589</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.626157</v>
+        <v>0.505651</v>
       </c>
       <c r="AM25" t="n">
-        <v>-37.38</v>
+        <v>-49.43</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -12261,10 +11253,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.245315</v>
+        <v>0.235304</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.9075</v>
+        <v>0.844</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -12416,7 +11408,7 @@
         <v>0</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.3929</v>
+        <v>0.3971</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -12445,7 +11437,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -12459,7 +11451,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -12478,7 +11470,7 @@
         <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0939</v>
       </c>
       <c r="L26" t="n">
         <v>0.4</v>
@@ -12493,13 +11485,13 @@
         <v>-0.0408</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0349</v>
+        <v>0.0411</v>
       </c>
       <c r="Q26" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0477</v>
+        <v>0.0584</v>
       </c>
       <c r="S26" t="n">
         <v>250</v>
@@ -12547,13 +11539,13 @@
         <v>-0.0785</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0283</v>
+        <v>0.0267</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.6853</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>10.97</v>
+        <v>10.76</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -12562,13 +11554,13 @@
         <v>-0.0037</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.020289</v>
+        <v>-0.000244</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.997523</v>
+        <v>1.032815</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.25</v>
+        <v>3.28</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -12598,10 +11590,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.079111</v>
+        <v>0.074591</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.2565</v>
+        <v>0.0033</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -12749,7 +11741,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3594</v>
+        <v>0.3464</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -12778,7 +11770,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -12804,14 +11796,14 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J27" t="n">
         <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0461</v>
+        <v>0.0459</v>
       </c>
       <c r="L27" t="n">
         <v>0.6364</v>
@@ -12829,13 +11821,13 @@
         <v>-0.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.1167</v>
+        <v>-0.1097</v>
       </c>
       <c r="S27" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T27" t="n">
         <v>0.5959</v>
@@ -12880,28 +11872,28 @@
         <v>0.1115</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.038</v>
+        <v>0.0369</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7096</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.97</v>
+        <v>3.88</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.0275</v>
+        <v>0.0274</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.06911399999999999</v>
+        <v>0.028489</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.492896</v>
+        <v>0.5408539999999999</v>
       </c>
       <c r="AM27" t="n">
-        <v>-50.71</v>
+        <v>-45.91</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -12931,10 +11923,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.106076</v>
+        <v>0.103046</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.6515</v>
+        <v>0.2765</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -12944,7 +11936,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -13082,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.3421</v>
+        <v>0.3112</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -13111,7 +12103,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -13144,37 +12136,37 @@
         <v>139</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2914</v>
+        <v>0.2902</v>
       </c>
       <c r="L28" t="n">
         <v>0.6331</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3972</v>
+        <v>0.3862</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9479</v>
+        <v>0.952</v>
       </c>
       <c r="O28" t="n">
         <v>0.1699</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0191</v>
+        <v>0.0214</v>
       </c>
       <c r="Q28" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1381</v>
+        <v>0.1421</v>
       </c>
       <c r="S28" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2772</v>
+        <v>0.2788</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0611</v>
+        <v>0.0602</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -13198,10 +12190,10 @@
         <v>0.5072</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.2762</v>
+        <v>0.2778</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.349</v>
+        <v>0.3507</v>
       </c>
       <c r="AC28" t="n">
         <v>0.065</v>
@@ -13213,28 +12205,28 @@
         <v>0.1294</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0287</v>
+        <v>0.0267</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.6786</v>
+        <v>0.6091</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.0808</v>
+        <v>0.0809</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.02182</v>
+        <v>0.015322</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.886138</v>
+        <v>0.868484</v>
       </c>
       <c r="AM28" t="n">
-        <v>-11.39</v>
+        <v>-13.15</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -13264,10 +12256,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.08001900000000001</v>
+        <v>0.074547</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.2727</v>
+        <v>0.2055</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -13419,7 +12411,7 @@
         <v>1</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.4037</v>
+        <v>0.4109</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -13448,7 +12440,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -13481,13 +12473,13 @@
         <v>131</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2746</v>
+        <v>0.2735</v>
       </c>
       <c r="L29" t="n">
         <v>0.7328</v>
       </c>
       <c r="M29" t="n">
-        <v>0.306</v>
+        <v>0.3037</v>
       </c>
       <c r="N29" t="n">
         <v>0.9288999999999999</v>
@@ -13496,13 +12488,13 @@
         <v>-0.1479</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0327</v>
+        <v>0.0291</v>
       </c>
       <c r="Q29" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0327</v>
+        <v>0.0291</v>
       </c>
       <c r="S29" t="n">
         <v>297</v>
@@ -13511,7 +12503,7 @@
         <v>0.1613</v>
       </c>
       <c r="U29" t="n">
-        <v>0.055</v>
+        <v>0.0548</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -13550,28 +12542,28 @@
         <v>0.056</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0152</v>
+        <v>0.013</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.3168</v>
+        <v>0.1951</v>
       </c>
       <c r="AH29" t="n">
-        <v>14.57</v>
+        <v>14.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.0443</v>
+        <v>0.0441</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.032055</v>
+        <v>0.024142</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.148631</v>
+        <v>1.187845</v>
       </c>
       <c r="AM29" t="n">
-        <v>14.86</v>
+        <v>18.78</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
@@ -13601,10 +12593,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.042285</v>
+        <v>0.03635</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.7581</v>
+        <v>0.6642</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -13752,7 +12744,7 @@
         <v>1</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4559</v>
+        <v>0.4709</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -13781,7 +12773,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -13790,7 +12782,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -13799,56 +12791,56 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>monitorar_e6_quase_nivel_a</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1464</v>
+        <v>0.1482</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7857</v>
+        <v>0.7887</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2297</v>
+        <v>0.2267</v>
       </c>
       <c r="N30" t="n">
         <v>0.4201</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.1578</v>
+        <v>-0.1615</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.02</v>
+        <v>-0.0142</v>
       </c>
       <c r="Q30" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.02</v>
+        <v>-0.0142</v>
       </c>
       <c r="S30" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.0292</v>
+        <v>-0.0311</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0348</v>
+        <v>0.0343</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -13872,52 +12864,52 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.0302</v>
+        <v>-0.0321</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.0068</v>
+        <v>0.008</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.0042</v>
+        <v>0.0045</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0217</v>
+        <v>0.0245</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0122</v>
+        <v>0.0117</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3062</v>
+        <v>0.2698</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.79</v>
+        <v>18.92</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.0043</v>
+        <v>-0.0046</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.06398</v>
+        <v>0.055746</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.109768</v>
+        <v>1.121181</v>
       </c>
       <c r="AM30" t="n">
-        <v>10.98</v>
+        <v>12.12</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -13935,13 +12927,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.03397</v>
+        <v>0.032563</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.8834</v>
+        <v>1.7119</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -13956,7 +12948,7 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC30" t="n">
@@ -14089,10 +13081,10 @@
         <v>0</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5897</v>
+        <v>0.5799</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.2948</v>
+        <v>0.5799</v>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
@@ -14130,7 +13122,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -14163,7 +13155,7 @@
         <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0314</v>
+        <v>0.0313</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -14178,16 +13170,16 @@
         <v>-0.18</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1497</v>
+        <v>0.1446</v>
       </c>
       <c r="Q31" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2524</v>
+        <v>0.2477</v>
       </c>
       <c r="S31" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T31" t="n">
         <v>-0.18</v>
@@ -14232,13 +13224,13 @@
         <v>-0.2521</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0148</v>
+        <v>0.0142</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3</v>
+        <v>0.2694</v>
       </c>
       <c r="AH31" t="n">
-        <v>26.21</v>
+        <v>26.15</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -14247,19 +13239,19 @@
         <v>-0.0056</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.017558</v>
+        <v>0.016579</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.028221</v>
+        <v>1.052269</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.82</v>
+        <v>5.23</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="n">
         <v>0</v>
@@ -14283,10 +13275,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.041376</v>
+        <v>0.039595</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.4243</v>
+        <v>0.4187</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -14434,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.4646</v>
+        <v>0.4701</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -14463,7 +13455,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -14496,7 +13488,7 @@
         <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0377</v>
+        <v>0.0376</v>
       </c>
       <c r="L32" t="n">
         <v>0.2222</v>
@@ -14511,16 +13503,16 @@
         <v>2.3291</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.125</v>
+        <v>-0.1475</v>
       </c>
       <c r="Q32" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.1475</v>
+        <v>-0.18</v>
       </c>
       <c r="S32" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="T32" t="n">
         <v>0.3916</v>
@@ -14561,28 +13553,28 @@
         <v>-0.0619</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0199</v>
+        <v>0.0187</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.4265</v>
+        <v>0.3663</v>
       </c>
       <c r="AH32" t="n">
-        <v>33.17</v>
+        <v>33.3</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.0148</v>
+        <v>0.0147</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.007391</v>
+        <v>0.008548</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.779375</v>
+        <v>0.7759470000000001</v>
       </c>
       <c r="AM32" t="n">
-        <v>-22.06</v>
+        <v>-22.41</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
@@ -14612,10 +13604,10 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.055626</v>
+        <v>0.052264</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.1329</v>
+        <v>0.1636</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -14763,7 +13755,7 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.3889</v>
+        <v>0.404</v>
       </c>
       <c r="CQ32" t="n">
         <v>0</v>
@@ -14792,7 +13784,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -14825,37 +13817,37 @@
         <v>66</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1384</v>
+        <v>0.1378</v>
       </c>
       <c r="L33" t="n">
-        <v>0.303</v>
+        <v>0.3182</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1667</v>
+        <v>0.1642</v>
       </c>
       <c r="N33" t="n">
         <v>0.9697</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.0135</v>
+        <v>-0.0968</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.033</v>
+        <v>-0.0347</v>
       </c>
       <c r="Q33" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.0277</v>
+        <v>-0.0312</v>
       </c>
       <c r="S33" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="T33" t="n">
         <v>0.0168</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0669</v>
+        <v>0.0664</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -14894,13 +13886,13 @@
         <v>-0.08550000000000001</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2666</v>
+        <v>0.2227</v>
       </c>
       <c r="AH33" t="n">
-        <v>21.25</v>
+        <v>21.18</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -14909,13 +13901,13 @@
         <v>0.0023</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.02605</v>
+        <v>0.015753</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.934318</v>
+        <v>0.959952</v>
       </c>
       <c r="AM33" t="n">
-        <v>-6.57</v>
+        <v>-4</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -14945,10 +13937,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.053034</v>
+        <v>0.05031</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.4912</v>
+        <v>0.3131</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -15100,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4737</v>
+        <v>0.4646</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -15129,7 +14121,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -15155,14 +14147,14 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J34" t="n">
         <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0523</v>
+        <v>0.0522</v>
       </c>
       <c r="L34" t="n">
         <v>0.28</v>
@@ -15177,10 +14169,10 @@
         <v>0.5239</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0702</v>
+        <v>0.0614</v>
       </c>
       <c r="Q34" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R34" t="n">
         <v>0.1603</v>
@@ -15231,13 +14223,13 @@
         <v>-0.0747</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0153</v>
+        <v>0.0147</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.3554</v>
+        <v>0.3292</v>
       </c>
       <c r="AH34" t="n">
-        <v>27.42</v>
+        <v>27.23</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -15246,13 +14238,13 @@
         <v>0.0015</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.024673</v>
+        <v>0.024821</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.963763</v>
+        <v>0.976729</v>
       </c>
       <c r="AM34" t="n">
-        <v>-3.62</v>
+        <v>-2.33</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -15264,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
         <v>1.033797</v>
@@ -15282,10 +14274,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.042622</v>
+        <v>0.041107</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.5789</v>
+        <v>0.6038</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -15295,7 +14287,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -15437,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.429</v>
+        <v>0.4367</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -15466,7 +14458,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -15499,7 +14491,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0419</v>
+        <v>0.0418</v>
       </c>
       <c r="L35" t="n">
         <v>0.85</v>
@@ -15514,16 +14506,16 @@
         <v>0.2618</v>
       </c>
       <c r="P35" t="n">
-        <v>0.5651</v>
+        <v>0.5594</v>
       </c>
       <c r="Q35" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8237</v>
+        <v>0.8186</v>
       </c>
       <c r="S35" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T35" t="n">
         <v>0.2617</v>
@@ -15564,28 +14556,28 @@
         <v>0.1567</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0207</v>
+        <v>0.0186</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.3022</v>
+        <v>0.2469</v>
       </c>
       <c r="AH35" t="n">
-        <v>55.2</v>
+        <v>54.21</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.011</v>
+        <v>0.0109</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.050463</v>
+        <v>-0.06184</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.85851</v>
+        <v>0.899316</v>
       </c>
       <c r="AM35" t="n">
-        <v>-14.15</v>
+        <v>-10.07</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -15615,10 +14607,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.057707</v>
+        <v>0.051993</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.8745000000000001</v>
+        <v>1.1894</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -15766,7 +14758,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.485</v>
+        <v>0.5275</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -15795,7 +14787,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -15828,10 +14820,10 @@
         <v>42</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0881</v>
+        <v>0.0877</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="M36" t="n">
         <v>0.2222</v>
@@ -15846,19 +14838,19 @@
         <v>-0.168</v>
       </c>
       <c r="Q36" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.0547</v>
+        <v>-0.0643</v>
       </c>
       <c r="S36" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.0342</v>
+        <v>-0.0319</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0466</v>
+        <v>0.0465</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -15882,43 +14874,43 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.0352</v>
+        <v>-0.0329</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.0178</v>
+        <v>-0.0114</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.0098</v>
+        <v>-0.0072</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.0022</v>
+        <v>0.0042</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0425</v>
+        <v>0.0403</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.7672</v>
+        <v>0.6925</v>
       </c>
       <c r="AH36" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>-0.003</v>
+        <v>-0.0028</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.100723</v>
+        <v>0.112478</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.96071</v>
+        <v>0.988289</v>
       </c>
       <c r="AM36" t="n">
-        <v>-3.93</v>
+        <v>-1.17</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -15930,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
         <v>1.03</v>
@@ -15942,16 +14934,16 @@
         <v>0.97</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV36" t="n">
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.118506</v>
+        <v>0.112467</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.8499</v>
+        <v>1.0001</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -15966,7 +14958,7 @@
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC36" t="n">
@@ -16099,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.4211</v>
+        <v>0.4511</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -16128,7 +15120,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -16161,7 +15153,7 @@
         <v>65</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1368</v>
+        <v>0.1363</v>
       </c>
       <c r="L37" t="n">
         <v>0.7846</v>
@@ -16176,10 +15168,10 @@
         <v>-0.18</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.1701</v>
+        <v>-0.1768</v>
       </c>
       <c r="Q37" t="n">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="R37" t="n">
         <v>-0.0815</v>
@@ -16226,13 +15218,13 @@
         <v>-0.0021</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.015</v>
+        <v>0.0135</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.3885</v>
+        <v>0.3155</v>
       </c>
       <c r="AH37" t="n">
-        <v>26.65</v>
+        <v>26.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -16241,13 +15233,13 @@
         <v>0.0119</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.014753</v>
+        <v>0.00665</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.87465</v>
+        <v>0.876444</v>
       </c>
       <c r="AM37" t="n">
-        <v>-12.53</v>
+        <v>-12.36</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -16277,10 +15269,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.041808</v>
+        <v>0.037743</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.3529</v>
+        <v>0.1762</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -16428,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4381</v>
+        <v>0.435</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -16457,7 +15449,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -16490,7 +15482,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1551</v>
+        <v>0.1545</v>
       </c>
       <c r="L38" t="n">
         <v>0.3649</v>
@@ -16508,7 +15500,7 @@
         <v>-0.18</v>
       </c>
       <c r="Q38" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R38" t="n">
         <v>-0.18</v>
@@ -16555,28 +15547,28 @@
         <v>-0.0549</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0295</v>
+        <v>0.0279</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.5945</v>
+        <v>0.5412</v>
       </c>
       <c r="AH38" t="n">
-        <v>34.69</v>
+        <v>34.45</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.0147</v>
+        <v>0.0146</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.067578</v>
+        <v>0.06412</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.895102</v>
+        <v>0.942049</v>
       </c>
       <c r="AM38" t="n">
-        <v>-10.49</v>
+        <v>-5.8</v>
       </c>
       <c r="AN38" t="n">
         <v>0</v>
@@ -16606,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.08237999999999999</v>
+        <v>0.07788299999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.8203</v>
+        <v>0.8233</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -16761,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.4337</v>
+        <v>0.4446</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -16790,7 +15782,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -16816,7 +15808,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -16838,13 +15830,13 @@
         <v>-0.18</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.1516</v>
+        <v>-0.1498</v>
       </c>
       <c r="Q39" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.158</v>
+        <v>-0.1291</v>
       </c>
       <c r="S39" t="n">
         <v>230</v>
@@ -16892,13 +15884,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0221</v>
+        <v>0.0209</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.7226</v>
+        <v>0.6484</v>
       </c>
       <c r="AH39" t="n">
-        <v>15.08</v>
+        <v>14.95</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -16907,13 +15899,13 @@
         <v>-0.0011</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.051012</v>
+        <v>0.035318</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.783863</v>
+        <v>0.86557</v>
       </c>
       <c r="AM39" t="n">
-        <v>-21.61</v>
+        <v>-13.44</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -16937,16 +15929,16 @@
         <v>0.938659</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.061534</v>
+        <v>0.058408</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.829</v>
+        <v>0.6047</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -16956,7 +15948,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -17098,7 +16090,7 @@
         <v>1</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.4582</v>
+        <v>0.4506</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -17127,7 +16119,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -17160,7 +16152,7 @@
         <v>173</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3619</v>
+        <v>0.3612</v>
       </c>
       <c r="L40" t="n">
         <v>0.4971</v>
@@ -17175,16 +16167,16 @@
         <v>0.051</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.0487</v>
+        <v>-0.0393</v>
       </c>
       <c r="Q40" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.0283</v>
+        <v>-0.0247</v>
       </c>
       <c r="S40" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T40" t="n">
         <v>0.1016</v>
@@ -17225,28 +16217,28 @@
         <v>-0.0004</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0163</v>
+        <v>0.0157</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.4592</v>
+        <v>0.4205</v>
       </c>
       <c r="AH40" t="n">
-        <v>48.34</v>
+        <v>48.61</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.0368</v>
+        <v>0.0367</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.019357</v>
+        <v>-0.016525</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.063547</v>
+        <v>1.073749</v>
       </c>
       <c r="AM40" t="n">
-        <v>6.35</v>
+        <v>7.37</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -17276,10 +16268,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.045575</v>
+        <v>0.04393</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.4247</v>
+        <v>0.3762</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -17431,7 +16423,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.428</v>
+        <v>0.4308</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -17460,7 +16452,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -17490,40 +16482,40 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1635</v>
+        <v>0.167</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8462</v>
+        <v>0.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5889</v>
+        <v>0.6044</v>
       </c>
       <c r="N41" t="n">
-        <v>1.2954</v>
+        <v>1.3214</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8733</v>
+        <v>0.9082</v>
       </c>
       <c r="P41" t="n">
-        <v>0.0118</v>
+        <v>0.0141</v>
       </c>
       <c r="Q41" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0804</v>
+        <v>0.0809</v>
       </c>
       <c r="S41" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T41" t="n">
-        <v>0.8155</v>
+        <v>0.845</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0983</v>
+        <v>0.0987</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -17541,49 +16533,49 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>0.3861</v>
+        <v>0.3917</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5128</v>
+        <v>1.535</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.8145</v>
+        <v>0.844</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.003</v>
+        <v>1.0343</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.2022</v>
+        <v>0.2054</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.238</v>
+        <v>0.2409</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.3861</v>
+        <v>0.3917</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0764</v>
+        <v>0.1072</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.6824</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.1334</v>
+        <v>0.1411</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.441249</v>
+        <v>-0.277978</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.966432</v>
+        <v>0.750288</v>
       </c>
       <c r="AM41" t="n">
-        <v>-3.36</v>
+        <v>-24.97</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -17595,7 +16587,7 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR41" t="n">
         <v>1.039087</v>
@@ -17607,16 +16599,16 @@
         <v>0.811768</v>
       </c>
       <c r="AU41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.21315</v>
+        <v>0.29929</v>
       </c>
       <c r="AX41" t="n">
-        <v>2.0701</v>
+        <v>0.9288</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -17764,7 +16756,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.5514</v>
+        <v>0.3808</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -17793,7 +16785,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -17826,7 +16818,7 @@
         <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0731</v>
       </c>
       <c r="L42" t="n">
         <v>0.4857</v>
@@ -17841,16 +16833,16 @@
         <v>0.3394</v>
       </c>
       <c r="P42" t="n">
-        <v>-0</v>
+        <v>0.0038</v>
       </c>
       <c r="Q42" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3227</v>
+        <v>0.3299</v>
       </c>
       <c r="S42" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T42" t="n">
         <v>0.1134</v>
@@ -17891,13 +16883,13 @@
         <v>0.0712</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0196</v>
+        <v>0.018</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.503</v>
+        <v>0.4277</v>
       </c>
       <c r="AH42" t="n">
-        <v>18.74</v>
+        <v>18.75</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -17906,13 +16898,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.053313</v>
+        <v>0.052147</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.951693</v>
+        <v>0.948499</v>
       </c>
       <c r="AM42" t="n">
-        <v>-4.83</v>
+        <v>-5.15</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -17942,10 +16934,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.054714</v>
+        <v>0.050316</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.9744</v>
+        <v>1.0364</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -18097,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.5065</v>
+        <v>0.5278</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -18126,7 +17118,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -18135,7 +17127,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -18144,26 +17136,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J43" t="n">
         <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0839</v>
+        <v>0.0835</v>
       </c>
       <c r="L43" t="n">
         <v>0.525</v>
@@ -18172,28 +17160,28 @@
         <v>0.2642</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5604</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O43" t="n">
         <v>0.1488</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.1423</v>
+        <v>-0.1362</v>
       </c>
       <c r="Q43" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0348</v>
+        <v>0.0371</v>
       </c>
       <c r="S43" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0864</v>
+        <v>0.0859</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0585</v>
+        <v>0.0584</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -18207,16 +17195,16 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.1319</v>
+        <v>0.1313</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.412</v>
+        <v>0.4104</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0854</v>
+        <v>0.0849</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.1319</v>
+        <v>0.1313</v>
       </c>
       <c r="AC43" t="n">
         <v>0.0477</v>
@@ -18228,28 +17216,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0243</v>
+        <v>0.0229</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2705</v>
+        <v>0.1964</v>
       </c>
       <c r="AH43" t="n">
-        <v>8.33</v>
+        <v>8.34</v>
       </c>
       <c r="AI43" t="n">
-        <v>7.86</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.0072</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.056147</v>
+        <v>-0.025083</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.334733</v>
+        <v>1.383134</v>
       </c>
       <c r="AM43" t="n">
-        <v>33.47</v>
+        <v>38.31</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -18276,13 +17264,13 @@
         <v>1</v>
       </c>
       <c r="AV43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.06793100000000001</v>
+        <v>0.063846</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.8265</v>
+        <v>0.3929</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -18292,7 +17280,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -18430,71 +17418,27 @@
         <v>0</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.4639</v>
+        <v>0.4353</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.4639</v>
-      </c>
-      <c r="CR43" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS43" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT43" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU43" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV43" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW43" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.085 | spread_35_20: esp=+0.048 | spread_45_25: esp=+0.049 | spread_45_15: esp=+0.086</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR43" t="inlineStr"/>
+      <c r="CS43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr"/>
+      <c r="CU43" t="inlineStr"/>
+      <c r="CV43" t="inlineStr"/>
+      <c r="CW43" t="inlineStr"/>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.132 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY43" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="CZ43" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.052%/dia | carry 20 pregões: 1.05%]</t>
-        </is>
-      </c>
-      <c r="DA43" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB43" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC43" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY43" t="inlineStr"/>
+      <c r="CZ43" t="inlineStr"/>
+      <c r="DA43" t="inlineStr"/>
+      <c r="DB43" t="inlineStr"/>
+      <c r="DC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18503,7 +17447,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -18536,7 +17480,7 @@
         <v>47</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0985</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>0.617</v>
@@ -18554,13 +17498,13 @@
         <v>0.0398</v>
       </c>
       <c r="Q44" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0425</v>
+        <v>0.0372</v>
       </c>
       <c r="S44" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T44" t="n">
         <v>1.1514</v>
@@ -18605,28 +17549,28 @@
         <v>0.2183</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.7574</v>
+        <v>0.6538</v>
       </c>
       <c r="AH44" t="n">
-        <v>6.96</v>
+        <v>6.84</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.1135</v>
+        <v>0.113</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.045945</v>
+        <v>0.031029</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.656698</v>
+        <v>0.758026</v>
       </c>
       <c r="AM44" t="n">
-        <v>-34.33</v>
+        <v>-24.2</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -18650,16 +17594,16 @@
         <v>0.8942099999999999</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.094957</v>
+        <v>0.08643099999999999</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.4839</v>
+        <v>0.359</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -18811,7 +17755,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.3635</v>
+        <v>0.3717</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -18840,7 +17784,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -18873,7 +17817,7 @@
         <v>44</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0922</v>
+        <v>0.0919</v>
       </c>
       <c r="L45" t="n">
         <v>0.4545</v>
@@ -18891,7 +17835,7 @@
         <v>-0.0166</v>
       </c>
       <c r="Q45" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R45" t="n">
         <v>-0.0228</v>
@@ -18942,28 +17886,28 @@
         <v>-0.1007</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0151</v>
+        <v>0.0144</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.4239</v>
+        <v>0.3827</v>
       </c>
       <c r="AH45" t="n">
-        <v>29.39</v>
+        <v>29.59</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>-0.0117</v>
+        <v>-0.0116</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.031531</v>
+        <v>-0.031626</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.094267</v>
+        <v>1.101418</v>
       </c>
       <c r="AM45" t="n">
-        <v>9.43</v>
+        <v>10.14</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -18993,10 +17937,10 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.042017</v>
+        <v>0.040095</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.7504</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -19148,7 +18092,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.475</v>
+        <v>0.4871</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -19177,7 +18121,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -19225,16 +18169,16 @@
         <v>-0.18</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0114</v>
+        <v>0.0161</v>
       </c>
       <c r="Q46" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1495</v>
+        <v>0.1526</v>
       </c>
       <c r="S46" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T46" t="n">
         <v>-0.18</v>
@@ -19279,13 +18223,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0319</v>
+        <v>0.0297</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.6793</v>
       </c>
       <c r="AH46" t="n">
-        <v>14.32</v>
+        <v>14.35</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -19294,13 +18238,13 @@
         <v>-0.0015</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.08924700000000001</v>
+        <v>0.089305</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.956936</v>
+        <v>0.973264</v>
       </c>
       <c r="AM46" t="n">
-        <v>-4.31</v>
+        <v>-2.67</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -19324,16 +18268,16 @@
         <v>0.954628</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV46" t="n">
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.08892</v>
+        <v>0.082866</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.0037</v>
+        <v>1.0777</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -19481,7 +18425,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.42</v>
+        <v>0.439</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -37985,12 +36929,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -38093,7 +37037,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -38309,7 +37253,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -38345,7 +37289,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -38417,7 +37361,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -38525,7 +37469,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -38633,7 +37577,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -38813,7 +37757,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -38921,12 +37865,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>monitorar_e6_quase_nivel_a</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -39065,7 +38009,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -39245,7 +38189,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -39389,12 +38333,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -39669,7 +38613,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.5399</v>
+        <v>0.5293</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -39735,7 +38679,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.4687</v>
+        <v>0.4749</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -39884,16 +38828,16 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.6017</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -40005,7 +38949,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.3783</v>
+        <v>0.3767</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -40071,7 +39015,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.4827</v>
+        <v>0.4673</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -40271,15 +39215,15 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4343</v>
+        <v>0.4744</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -40341,7 +39285,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.3709</v>
+        <v>0.319</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -40499,7 +39443,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.4154</v>
+        <v>0.4174</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -40565,7 +39509,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.5309</v>
+        <v>0.5334</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -40723,7 +39667,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.2874</v>
+        <v>0.325</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -40819,7 +39763,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -40835,7 +39779,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4556</v>
+        <v>0.4765</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -40844,7 +39788,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -40897,15 +39841,15 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.3302</v>
+        <v>0.3529</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -41097,15 +40041,15 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.5153</v>
+        <v>0.444</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -41213,7 +40157,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.482</v>
+        <v>0.5092</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -41275,15 +40219,15 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.4813</v>
+        <v>0.4293</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -41345,7 +40289,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.392</v>
+        <v>0.4326</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -41457,7 +40401,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.4921</v>
+        <v>0.5139</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -41550,7 +40494,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -41565,15 +40509,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>vol_live_sem_expansao</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.5406</v>
+        <v>0.4645</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -41622,7 +40566,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -41635,7 +40579,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.3506</v>
+        <v>0.3665</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -41747,7 +40691,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.3506</v>
+        <v>0.3586</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -41794,7 +40738,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -41809,15 +40753,15 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.3374</v>
+        <v>0.3636</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -42063,7 +41007,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.5276</v>
+        <v>0.5395</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -42129,7 +41073,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.584</v>
+        <v>0.4781</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -42195,7 +41139,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.3929</v>
+        <v>0.3971</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -42261,7 +41205,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.3594</v>
+        <v>0.3464</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -42446,7 +41390,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -42461,15 +41405,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.3421</v>
+        <v>0.3112</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -42531,7 +41475,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.4037</v>
+        <v>0.4109</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -42597,7 +41541,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.4559</v>
+        <v>0.4709</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -42654,16 +41598,16 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>monitorar_e6_quase_nivel_a</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5897</v>
+        <v>0.5799</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -42672,7 +41616,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -42729,7 +41673,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4646</v>
+        <v>0.4701</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -43025,7 +41969,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.3889</v>
+        <v>0.404</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -43413,7 +42357,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.4737</v>
+        <v>0.4646</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -43506,7 +42450,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -43521,15 +42465,15 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.429</v>
+        <v>0.4367</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -43591,7 +42535,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.485</v>
+        <v>0.5275</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -43683,10 +42627,10 @@
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -43699,7 +42643,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.4211</v>
+        <v>0.4511</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -43708,7 +42652,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -43853,7 +42797,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.4381</v>
+        <v>0.435</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -43919,7 +42863,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.4337</v>
+        <v>0.4446</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -43972,7 +42916,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -43981,15 +42925,15 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.4582</v>
+        <v>0.4506</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -44051,7 +42995,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.428</v>
+        <v>0.4308</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -44368,7 +43312,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -44381,7 +43325,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.5514</v>
+        <v>0.3808</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -44581,7 +43525,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5065</v>
+        <v>0.5278</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -44628,7 +43572,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -44638,20 +43582,20 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.4639</v>
+        <v>0.4353</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -44792,7 +43736,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -44805,7 +43749,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3635</v>
+        <v>0.3717</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -44917,7 +43861,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.475</v>
+        <v>0.4871</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -44970,7 +43914,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -44983,7 +43927,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.42</v>
+        <v>0.439</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -45144,7 +44088,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/home/runner/work/mia_telegram/mia_telegram/saidas/direction/direction_best_2026_08_19.xlsx</t>
+          <t>/home/ghrunner/runner-mia_telegram/_work/mia_telegram/mia_telegram/saidas/direction/direction_best_2026_08_19.xlsx</t>
         </is>
       </c>
     </row>
@@ -45178,7 +44122,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/home/runner/work/mia_telegram/mia_telegram/saidas/volatility/volatility_best_2026_08_19_v6_2_operational.xlsx</t>
+          <t>/home/ghrunner/runner-mia_telegram/_work/mia_telegram/mia_telegram/saidas/volatility/volatility_best_2026_08_19_v6_2_operational.xlsx</t>
         </is>
       </c>
     </row>
@@ -45301,7 +44245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -45311,7 +44255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -45321,7 +44265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -45331,7 +44275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -45341,7 +44285,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -45361,7 +44305,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -45371,7 +44315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -45381,7 +44325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -45401,7 +44345,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -45421,7 +44365,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">

--- a/saidas/ordens_dia/ordem_dia_2026_08_28_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_08_28_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE3"/>
+  <dimension ref="A1:DE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,17 +985,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VETADA — esperança histórica insuficiente</t>
+          <t>Bull spread largo: compra call delta~45, venda call delta~15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1007,57 +1007,57 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1482</v>
+        <v>0.2735</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7887</v>
+        <v>0.7328</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2267</v>
+        <v>0.3015</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4201</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1615</v>
+        <v>-0.1479</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0142</v>
+        <v>0.0291</v>
       </c>
       <c r="R2" t="n">
         <v>459</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0142</v>
+        <v>0.0291</v>
       </c>
       <c r="T2" t="n">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0311</v>
+        <v>0.1613</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0343</v>
+        <v>0.0546</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1067,53 +1067,53 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>esperanca</t>
+          <t>risco</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>-0.18</v>
+        <v>0.056</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.2195</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.0321</v>
+        <v>0.1603</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.008</v>
+        <v>0.1933</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0045</v>
+        <v>0.0226</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0245</v>
+        <v>0.0241</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.028</v>
+        <v>0.056</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0117</v>
+        <v>0.0131</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2698</v>
+        <v>0.1987</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.92</v>
+        <v>14.68</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.43</v>
+        <v>15.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.0046</v>
+        <v>0.0441</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.055746</v>
+        <v>0.030556</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.121181</v>
+        <v>1.19085</v>
       </c>
       <c r="AN2" t="n">
-        <v>12.12</v>
+        <v>19.08</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1128,13 +1128,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.114031</v>
+        <v>1.121647</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.116819</v>
+        <v>1.121647</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.873772</v>
+        <v>0.846091</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
@@ -1143,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.032563</v>
+        <v>0.036522</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.7119</v>
+        <v>0.8366</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1165,20 +1165,20 @@
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BI2" t="n">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BP2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="BR2" t="n">
         <v>1</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1224,54 +1224,54 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>exec_expansion_har</t>
+          <t>expansion_moderada_har</t>
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.647</v>
+        <v>0.6813</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.6573</v>
+        <v>0.5794</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.4975</v>
+        <v>0.5092</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.3779308827479717</v>
+        <v>0.3024599318039676</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.6219595510964607</v>
+        <v>0.6186865392486181</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.1817909218890814</v>
+        <v>0.3928411107741939</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.6219595510964607</v>
+        <v>0.6186865392486181</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.5503875968992248</v>
+        <v>1</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.5546875</v>
+        <v>0.03937007874015748</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.6408450704225352</v>
+        <v>1</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.5481927710843374</v>
+        <v>0.02890173410404624</v>
       </c>
       <c r="CH2" t="n">
-        <v>0</v>
+        <v>0.2145748987854251</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>0.828125</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>har_fallback_aprovado_expansao</t>
+          <t>har_fallback_moderado</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1288,44 +1288,76 @@
         <v>1</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.9375</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5799</v>
+        <v>0.4874</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5799</v>
+        <v>0.4874</v>
       </c>
       <c r="CS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Call naked delta~45 (se rv_rank &lt; 0.60)</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Bull spread estreito: compra delta~45, venda delta~25</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Spread ainda mais largo que 45/15; ratio spread</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>~0.45 (perna longa)</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.160 | naked_45: esp=+0.193 | spread_35_20: esp=+0.023 | spread_45_25: esp=+0.024</t>
+        </is>
+      </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
+          <t>[Empírico] Bull spread largo: compra call delta~45, venda call delta~15 — esp_estrutura=0.056 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco (vol via HAR — naked vetado por risco).</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="inlineStr"/>
-      <c r="DD2" t="inlineStr"/>
-      <c r="DE2" t="inlineStr"/>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>OBRIGATÓRIO: débito ≤ 50% da largura entre strikes (ideal ≤ 33% para relação lucro/perda 2:1). Se débito &gt; 50%: aproximar strikes ou aguardar. rv_rank=0.20 — custo aceitável. [Carry 20 pregões: 1.05% — preferir spread bull/bear sobre naked para calls em carry alto]</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>50% do lucro máximo da trava</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>100% do débito pago</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Trava limita upside — sair em 50% do max. Stop = débito total.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1338,12 +1370,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Monitorar CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1357,56 +1389,56 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>monitorar_e6_quase_nivel_a</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0626</v>
+        <v>0.1482</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6667</v>
+        <v>0.7887</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3</v>
+        <v>0.2267</v>
       </c>
       <c r="O3" t="n">
-        <v>0.446</v>
+        <v>0.4201</v>
       </c>
       <c r="P3" t="n">
-        <v>0.126</v>
+        <v>-0.1629</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0226</v>
+        <v>-0.0142</v>
       </c>
       <c r="R3" t="n">
         <v>459</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1206</v>
+        <v>-0.0142</v>
       </c>
       <c r="T3" t="n">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0152</v>
+        <v>-0.0313</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0623</v>
+        <v>0.0343</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1415,7 +1447,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1430,76 +1462,76 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0142</v>
+        <v>-0.0323</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0553</v>
+        <v>0.0072</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0313</v>
+        <v>0.0037</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0358</v>
+        <v>0.0236</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0537</v>
+        <v>0.0271</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0136</v>
+        <v>0.0116</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2803</v>
+        <v>0.2672</v>
       </c>
       <c r="AI3" t="n">
-        <v>28.71</v>
+        <v>18.87</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>19.38</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.001</v>
+        <v>-0.0046</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.038179</v>
+        <v>0.054957</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.079039</v>
+        <v>1.122789</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.9</v>
+        <v>12.28</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.092646</v>
+        <v>1.114031</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.111283</v>
+        <v>1.116819</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.933225</v>
+        <v>0.873772</v>
       </c>
       <c r="AV3" t="n">
         <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.037934</v>
+        <v>0.032463</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.0065</v>
+        <v>1.6929</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1514,30 +1546,26 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="BI3" t="n">
         <v>1</v>
       </c>
@@ -1545,90 +1573,90 @@
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BP3" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="BR3" t="n">
         <v>1</v>
       </c>
       <c r="BS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>1</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>exec_expansion_alerta_gap</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.6855</v>
+        <v>0.647</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.604</v>
+        <v>0.6573</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.5331</v>
+        <v>0.4975</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.4500888526862044</v>
+        <v>0.3779308827479717</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.6043632288353558</v>
+        <v>0.6219595510964607</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.5321149388232496</v>
+        <v>0.1817909218890814</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.6043632288353558</v>
+        <v>0.6219595510964607</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.8</v>
+        <v>0.5503875968992248</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.183206106870229</v>
+        <v>0.5546875</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.6408450704225352</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3218390804597701</v>
+        <v>0.5481927710843374</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.6756756756756757</v>
+        <v>0</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1592356687898089</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>aprovado_alerta_gap_generalizacao</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1638,23 +1666,23 @@
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.5395</v>
+        <v>0.5785</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.2698</v>
+        <v>0.5785</v>
       </c>
       <c r="CS3" t="n">
         <v>1</v>
@@ -1683,6 +1711,363 @@
       <c r="DC3" t="inlineStr"/>
       <c r="DD3" t="inlineStr"/>
       <c r="DE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v5.5_executor_diario</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Monitorar CALL (VETADA)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>monitorar_e6_quase_nivel_a</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="R4" t="n">
+        <v>459</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="T4" t="n">
+        <v>353</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>nenhuma</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.039881</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.083631</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.092646</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.111283</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.933225</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.037688</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.0582</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>neutro_zona_cinza</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>52</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>exec_bilateral</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>exec_expansion_alerta_gap</t>
+        </is>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.6855</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.4500888526862044</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.6043632288353558</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.5321149388232496</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.6043632288353558</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.183206106870229</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.3218390804597701</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1592356687898089</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>aprovado_alerta_gap_generalizacao</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>threshold_por_ativo</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.5459000000000001</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>vetada</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1819,32 +2204,32 @@
         <v>0.66</v>
       </c>
       <c r="I2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="J2" t="n">
-        <v>-36.36</v>
+        <v>-39.39</v>
       </c>
       <c r="K2" t="n">
-        <v>1.26</v>
+        <v>1.374</v>
       </c>
       <c r="L2" t="n">
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.77</v>
+        <v>0.884</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.929</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.278</v>
+        <v>-0.317</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M=1.26 ≥ BE+alvo=0.79 | lucro≈+0.77DP</t>
+          <t>M=1.37 ≥ BE+alvo=0.79 | lucro≈+0.88DP</t>
         </is>
       </c>
     </row>
@@ -1882,32 +2267,32 @@
         <v>5.19</v>
       </c>
       <c r="I3" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.39</v>
+        <v>-14.77</v>
       </c>
       <c r="K3" t="n">
-        <v>1.412</v>
+        <v>1.435</v>
       </c>
       <c r="L3" t="n">
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.922</v>
+        <v>0.945</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.205</v>
+        <v>0.148</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0153</v>
+        <v>0.0111</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>M=1.41 ≥ BE+alvo=0.79 | lucro≈+0.92DP</t>
+          <t>M=1.44 ≥ BE+alvo=0.79 | lucro≈+0.95DP</t>
         </is>
       </c>
     </row>
@@ -1945,13 +2330,13 @@
         <v>26.05</v>
       </c>
       <c r="I4" t="n">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.82</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.904</v>
+        <v>-0.89</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
@@ -1963,14 +2348,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.456</v>
+        <v>0.48</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.031</v>
+        <v>-0.0326</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3d restantes — theta domina | M=-0.90 | lucro≈-0.32DP</t>
+          <t>3d restantes — theta domina | M=-0.89 | lucro≈-0.32DP</t>
         </is>
       </c>
     </row>
@@ -2008,13 +2393,13 @@
         <v>20.25</v>
       </c>
       <c r="I5" t="n">
-        <v>21.88</v>
+        <v>22.22</v>
       </c>
       <c r="J5" t="n">
-        <v>8.050000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.822</v>
+        <v>-1.142</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
@@ -2026,14 +2411,14 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.983</v>
+        <v>1.446</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0476</v>
+        <v>0.0645</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Modelo virou CALL | M=-0.82 | razao=0.98</t>
+          <t>Modelo virou CALL | M=-1.14 | razao=1.45</t>
         </is>
       </c>
     </row>
@@ -2071,13 +2456,13 @@
         <v>7.44</v>
       </c>
       <c r="I6" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="J6" t="n">
-        <v>18.95</v>
+        <v>18.82</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.806</v>
       </c>
       <c r="L6" t="n">
         <v>0.49</v>
@@ -2089,21 +2474,21 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1125</v>
+        <v>0.108</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Modelo virou CALL | M=-0.81 | razao=1.00</t>
+          <t>Modelo virou CALL | M=-0.81 | razao=0.96</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2112,7 +2497,7 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46248</v>
+        <v>46259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2125,22 +2510,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
-        <v>3.91</v>
+        <v>16.78</v>
       </c>
       <c r="I7" t="n">
-        <v>4.57</v>
+        <v>17.08</v>
       </c>
       <c r="J7" t="n">
-        <v>16.88</v>
+        <v>1.79</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.527</v>
+        <v>-0.033</v>
       </c>
       <c r="L7" t="n">
         <v>0.49</v>
@@ -2152,21 +2537,21 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0068</v>
+        <v>-0.0017</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>razao=0.05 &lt; 0.6 | M=-0.53 — ativo foi contra, tese falhou</t>
+          <t>razao=0.04 &lt; 0.6 | M=-0.03 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2175,7 +2560,7 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2188,22 +2573,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>46.57</v>
+        <v>3.91</v>
       </c>
       <c r="I8" t="n">
-        <v>48.61</v>
+        <v>4.62</v>
       </c>
       <c r="J8" t="n">
-        <v>4.38</v>
+        <v>18.16</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.405</v>
+        <v>-0.611</v>
       </c>
       <c r="L8" t="n">
         <v>0.49</v>
@@ -2215,30 +2600,30 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.376</v>
+        <v>0.099</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0165</v>
+        <v>0.0129</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>razao=0.38 &lt; 0.6 | M=-0.40 — ativo foi contra, tese falhou</t>
+          <t>razao=0.10 &lt; 0.6 | M=-0.61 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SINAL FRACO (segurar)</t>
+          <t>SINAL FRACO (reverter)</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2251,22 +2636,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>16.78</v>
+        <v>46.57</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>48.87</v>
       </c>
       <c r="J9" t="n">
-        <v>1.31</v>
+        <v>4.94</v>
       </c>
       <c r="K9" t="n">
-        <v>0.032</v>
+        <v>-0.473</v>
       </c>
       <c r="L9" t="n">
         <v>0.49</v>
@@ -2278,14 +2663,14 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03</v>
+        <v>0.329</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0013</v>
+        <v>-0.0147</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>razao=0.03 &lt; 0.6 | M=0.03 — movimento OK, modelo ruidoso</t>
+          <t>razao=0.33 &lt; 0.6 | M=-0.47 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -2386,13 +2771,13 @@
         <v>14.57</v>
       </c>
       <c r="I11" t="n">
-        <v>14.53</v>
+        <v>14.68</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.27</v>
+        <v>0.75</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.227</v>
+        <v>-0.05</v>
       </c>
       <c r="L11" t="n">
         <v>0.425</v>
@@ -2404,14 +2789,14 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.664</v>
+        <v>0.837</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0241</v>
+        <v>0.0306</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=-0.23 | razao=0.66 | 1/20d</t>
+          <t>M=-0.05 | razao=0.84 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -2449,13 +2834,13 @@
         <v>9.84</v>
       </c>
       <c r="I12" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="J12" t="n">
-        <v>4.98</v>
+        <v>5.89</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.253</v>
+        <v>-0.344</v>
       </c>
       <c r="L12" t="n">
         <v>0.425</v>
@@ -2467,14 +2852,14 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.781</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.053</v>
+        <v>-0.0464</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=-0.25 | razao=0.78 | 3/20d</t>
+          <t>M=-0.34 | razao=0.69 | 3/20d</t>
         </is>
       </c>
     </row>
@@ -2512,13 +2897,13 @@
         <v>79.11</v>
       </c>
       <c r="I13" t="n">
-        <v>77.84</v>
+        <v>78.58</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.61</v>
+        <v>-0.67</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.385</v>
+        <v>-0.265</v>
       </c>
       <c r="L13" t="n">
         <v>0.49</v>
@@ -2530,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.633</v>
+        <v>1.929</v>
       </c>
       <c r="P13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=-0.38 | razao=1.63 | 1/20d</t>
+          <t>M=-0.26 | razao=1.93 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -2575,28 +2960,28 @@
         <v>4.11</v>
       </c>
       <c r="I14" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="J14" t="n">
-        <v>3.89</v>
+        <v>5.84</v>
       </c>
       <c r="K14" t="n">
-        <v>0.301</v>
+        <v>0.254</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.189</v>
+        <v>-0.236</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.844</v>
+        <v>0.797</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1986</v>
+        <v>-0.1891</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2615,7 +3000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2728,19 +3113,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2698</v>
+        <v>0.1987</v>
       </c>
       <c r="D2" t="n">
-        <v>1.121181</v>
+        <v>1.19085</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2748,39 +3133,71 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.0311</v>
+        <v>0.1613</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>vetada</t>
+          <t>media</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>Bull spread largo: compra call delta~45, venda call delta~15</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OBRIGATÓRIO: débito ≤ 50% da largura entre strikes (ideal ≤ 33% para relação lucro/perda 2:1). Se débito &gt; 50%: aproximar strikes ou aguardar. rv_rank=0.20 — custo aceitável. [Carry 20 pregões: 1.05% — preferir spread bull/bear sobre naked para calls em carry alto]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>50% do lucro máximo da trava</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>100% do débito pago</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Trava limita upside — sair em 50% do max. Stop = débito total.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Call naked delta~45 (se rv_rank &lt; 0.60)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Bull spread estreito: compra delta~45, venda delta~25</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Spread ainda mais largo que 45/15; ratio spread</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>~0.45 (perna longa)</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
+          <t>[Empírico] Bull spread largo: compra call delta~45, venda call delta~15 — esp_estrutura=0.056 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco (vol via HAR — naked vetado por risco).</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0117</v>
+        <v>0.0131</v>
       </c>
       <c r="S2" t="n">
-        <v>18.6</v>
+        <v>20.8</v>
       </c>
       <c r="T2" t="n">
-        <v>20.8</v>
+        <v>24.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -2791,19 +3208,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Monitorar CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2803</v>
+        <v>0.2672</v>
       </c>
       <c r="D3" t="n">
-        <v>1.079039</v>
+        <v>1.122789</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2811,7 +3228,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.0152</v>
+        <v>-0.0313</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2837,15 +3254,78 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0136</v>
+        <v>0.0116</v>
       </c>
       <c r="S3" t="n">
-        <v>21.6</v>
+        <v>18.4</v>
       </c>
       <c r="T3" t="n">
-        <v>23.3</v>
+        <v>20.7</v>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EGIE3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Monitorar CALL (VETADA)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.083631</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>vetada</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -3844,13 +4324,13 @@
         <v>-0.0392</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0171</v>
+        <v>0.0174</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.445</v>
+        <v>0.4604</v>
       </c>
       <c r="AH3" t="n">
-        <v>43.36</v>
+        <v>43.55</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -3859,13 +4339,13 @@
         <v>-0.0026</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.026614</v>
+        <v>0.027901</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9609220000000001</v>
+        <v>0.9601460000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3.91</v>
+        <v>-3.99</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -3895,10 +4375,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.047673</v>
+        <v>0.048529</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5583</v>
+        <v>0.5749</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -4046,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.4749</v>
+        <v>0.4735</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -4173,13 +4653,13 @@
         <v>0.2632</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0154</v>
+        <v>0.0145</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4918</v>
+        <v>0.4468</v>
       </c>
       <c r="AH4" t="n">
-        <v>77.84</v>
+        <v>78.58</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -4188,13 +4668,13 @@
         <v>0.2282</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.06998699999999999</v>
+        <v>0.07792</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.014308</v>
+        <v>1.022951</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -4224,10 +4704,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.042866</v>
+        <v>0.040388</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.6327</v>
+        <v>1.9293</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -4379,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5936</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -4506,13 +4986,13 @@
         <v>0.1227</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0157</v>
+        <v>0.0159</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.4519</v>
+        <v>0.4643</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>17.08</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -4521,13 +5001,13 @@
         <v>0.0765</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.001302</v>
+        <v>-0.001745</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.140773</v>
+        <v>1.129167</v>
       </c>
       <c r="AM5" t="n">
-        <v>14.08</v>
+        <v>12.92</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
@@ -4557,10 +5037,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.043817</v>
+        <v>0.04427</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0297</v>
+        <v>0.0394</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -4712,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.3767</v>
+        <v>0.3752</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -5180,13 +5660,13 @@
         <v>-0.08260000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0206</v>
+        <v>0.0209</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3422</v>
+        <v>0.3574</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.91</v>
+        <v>16.04</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -5195,13 +5675,13 @@
         <v>-0.008800000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.050551</v>
+        <v>0.05084</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.029079</v>
+        <v>1.013044</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.91</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -5231,10 +5711,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.057348</v>
+        <v>0.058417</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.8815</v>
+        <v>0.8703</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -5386,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4744</v>
+        <v>0.4702</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -5517,13 +5997,13 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0478</v>
+        <v>0.0467</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.9488</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -5532,13 +6012,13 @@
         <v>0.0583</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.006846</v>
+        <v>0.012946</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.015978</v>
+        <v>1.026638</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -5568,10 +6048,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.133418</v>
+        <v>0.130382</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0513</v>
+        <v>0.0993</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -5723,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.319</v>
+        <v>0.333</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -5854,13 +6334,13 @@
         <v>-0.0372</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0182</v>
+        <v>0.0186</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4115</v>
+        <v>0.431</v>
       </c>
       <c r="AH9" t="n">
-        <v>47.94</v>
+        <v>48.25</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -5869,13 +6349,13 @@
         <v>0.0069</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.004921</v>
+        <v>0.007318</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.059267</v>
+        <v>1.050414</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.93</v>
+        <v>5.04</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -5905,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.05066</v>
+        <v>0.051829</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1412</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -6060,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.4174</v>
+        <v>0.4179</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -6191,13 +6671,13 @@
         <v>0.3263</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0183</v>
+        <v>0.0185</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2962</v>
+        <v>0.3027</v>
       </c>
       <c r="AH10" t="n">
-        <v>46.15</v>
+        <v>45.99</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -6206,13 +6686,13 @@
         <v>0.0477</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.08000599999999999</v>
+        <v>0.075624</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.018475</v>
+        <v>1.015867</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -6242,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.051166</v>
+        <v>0.051752</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.5637</v>
+        <v>1.4613</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -6393,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.5334</v>
+        <v>0.5218</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -6524,13 +7004,13 @@
         <v>0.1691</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0244</v>
+        <v>0.0243</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.9029</v>
+        <v>0.8982</v>
       </c>
       <c r="AH11" t="n">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -6539,13 +7019,13 @@
         <v>0.0634</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.030993</v>
+        <v>-0.032566</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.805027</v>
+        <v>0.805125</v>
       </c>
       <c r="AM11" t="n">
-        <v>-19.5</v>
+        <v>-19.49</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -6575,10 +7055,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.068026</v>
+        <v>0.06782299999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.4556</v>
+        <v>0.4802</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6730,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.325</v>
+        <v>0.3284</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -6857,13 +7337,13 @@
         <v>0.1485</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5557</v>
+        <v>0.5686</v>
       </c>
       <c r="AH12" t="n">
-        <v>10.62</v>
+        <v>10.7</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -6872,13 +7352,13 @@
         <v>0.0134</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.081173</v>
+        <v>-0.07907</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.026378</v>
+        <v>1.018995</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -6908,10 +7388,10 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.074438</v>
+        <v>0.075169</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.0905</v>
+        <v>1.0519</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -7059,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.4765</v>
+        <v>0.4701</v>
       </c>
       <c r="CQ12" t="n">
         <v>0</v>
@@ -7201,13 +7681,13 @@
         <v>0.0014</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.030878</v>
+        <v>0.030897</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.945589</v>
+        <v>0.940306</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.44</v>
+        <v>-5.97</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -7240,7 +7720,7 @@
         <v>0.038046</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.8116</v>
+        <v>0.8121</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7443,7 +7923,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -7519,13 +7999,13 @@
         <v>-0.0764</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0392</v>
+        <v>0.0387</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6681</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -7534,13 +8014,13 @@
         <v>-0.0143</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.086636</v>
+        <v>0.087917</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.866666</v>
+        <v>0.8700639999999999</v>
       </c>
       <c r="AM14" t="n">
-        <v>-13.33</v>
+        <v>-12.99</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -7570,10 +8050,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.109355</v>
+        <v>0.10797</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.7922</v>
+        <v>0.8143</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7583,7 +8063,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -7725,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.444</v>
+        <v>0.4497</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -7856,13 +8336,13 @@
         <v>-0.0496</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0094</v>
+        <v>0.0095</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>15.07</v>
+        <v>15.19</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -7871,13 +8351,13 @@
         <v>0.0046</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.010584</v>
+        <v>-0.007615</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.283486</v>
+        <v>1.278294</v>
       </c>
       <c r="AM15" t="n">
-        <v>28.35</v>
+        <v>27.83</v>
       </c>
       <c r="AN15" t="n">
         <v>1</v>
@@ -7907,10 +8387,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.026341</v>
+        <v>0.026615</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.4018</v>
+        <v>0.2861</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -8062,7 +8542,7 @@
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.5092</v>
+        <v>0.4976</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -8117,7 +8597,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -8177,13 +8657,13 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.0423</v>
+        <v>0.0397</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.6862</v>
+        <v>0.6196</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.08</v>
+        <v>5.21</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -8192,13 +8672,13 @@
         <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.078058</v>
+        <v>0.103591</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.809048</v>
+        <v>0.842417</v>
       </c>
       <c r="AM16" t="n">
-        <v>-19.1</v>
+        <v>-15.76</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -8228,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.118055</v>
+        <v>0.110894</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.6612</v>
+        <v>0.9341</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -8241,7 +8721,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -8379,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4293</v>
+        <v>0.4699</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -8510,13 +8990,13 @@
         <v>-0.0704</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0268</v>
+        <v>0.0267</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.517</v>
+        <v>0.5133</v>
       </c>
       <c r="AH17" t="n">
-        <v>34.69</v>
+        <v>34.81</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -8525,13 +9005,13 @@
         <v>-0.001</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.021472</v>
+        <v>-0.021092</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.052432</v>
+        <v>1.052071</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -8561,10 +9041,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.074724</v>
+        <v>0.07446899999999999</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2874</v>
+        <v>0.2832</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -8712,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.4326</v>
+        <v>0.4329</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -8842,10 +9322,10 @@
         <v>0.0116</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4133</v>
+        <v>0.4131</v>
       </c>
       <c r="AH18" t="n">
-        <v>38.67</v>
+        <v>38.68</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -8854,13 +9334,13 @@
         <v>0.1346</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.038662</v>
+        <v>0.038386</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.95696</v>
+        <v>0.955474</v>
       </c>
       <c r="AM18" t="n">
-        <v>-4.3</v>
+        <v>-4.45</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -8890,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.032408</v>
+        <v>0.0324</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.193</v>
+        <v>1.1848</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -9045,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.5139</v>
+        <v>0.5131</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -9172,13 +9652,13 @@
         <v>0.1042</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0262</v>
+        <v>0.026</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.3107</v>
+        <v>0.3054</v>
       </c>
       <c r="AH19" t="n">
-        <v>22.97</v>
+        <v>23.02</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -9187,13 +9667,13 @@
         <v>0.0235</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.039257</v>
+        <v>0.037992</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.9741109999999999</v>
+        <v>0.9752</v>
       </c>
       <c r="AM19" t="n">
-        <v>-2.59</v>
+        <v>-2.48</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -9223,10 +9703,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.073184</v>
+        <v>0.072434</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.5364</v>
+        <v>0.5245</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -9378,7 +9858,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.4645</v>
+        <v>0.4643</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -9509,13 +9989,13 @@
         <v>0.1809</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0305</v>
+        <v>0.0304</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.6582</v>
+        <v>0.6542</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.28</v>
+        <v>19.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -9524,13 +10004,13 @@
         <v>0.029</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.027821</v>
+        <v>0.028967</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.776711</v>
+        <v>0.776959</v>
       </c>
       <c r="AM20" t="n">
-        <v>-22.33</v>
+        <v>-22.3</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -9560,10 +10040,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.085161</v>
+        <v>0.084874</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.3267</v>
+        <v>0.3413</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -9711,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.3665</v>
+        <v>0.3688</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -9782,7 +10262,7 @@
         <v>0.2312</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5185</v>
+        <v>0.5173</v>
       </c>
       <c r="O21" t="n">
         <v>0.0999</v>
@@ -9800,7 +10280,7 @@
         <v>382</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0112</v>
+        <v>-0.0114</v>
       </c>
       <c r="U21" t="n">
         <v>0.0258</v>
@@ -9827,10 +10307,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.0122</v>
+        <v>-0.0124</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.0246</v>
+        <v>-0.0249</v>
       </c>
       <c r="AC21" t="n">
         <v>-0.009599999999999999</v>
@@ -9842,28 +10322,28 @@
         <v>-0.0251</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0217</v>
+        <v>0.0218</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.7456</v>
+        <v>0.7516</v>
       </c>
       <c r="AH21" t="n">
-        <v>25.09</v>
+        <v>25.24</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.0043</v>
+        <v>-0.0044</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.015232</v>
+        <v>0.01574</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.827363</v>
+        <v>0.825055</v>
       </c>
       <c r="AM21" t="n">
-        <v>-17.26</v>
+        <v>-17.49</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -9893,10 +10373,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.06048</v>
+        <v>0.060769</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.2518</v>
+        <v>0.259</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -10048,7 +10528,7 @@
         <v>0</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.3586</v>
+        <v>0.3582</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -10179,13 +10659,13 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0243</v>
+        <v>0.024</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.9277</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>10.33</v>
+        <v>10.42</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -10194,13 +10674,13 @@
         <v>0.0443</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.052952</v>
+        <v>-0.04635</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.793277</v>
+        <v>0.802528</v>
       </c>
       <c r="AM22" t="n">
-        <v>-20.67</v>
+        <v>-19.75</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -10230,10 +10710,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.067786</v>
+        <v>0.067109</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.7812</v>
+        <v>0.6907</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -10385,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.3636</v>
+        <v>0.3579</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -10520,13 +11000,13 @@
         <v>0.0537</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0136</v>
+        <v>0.0135</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2803</v>
+        <v>0.2746</v>
       </c>
       <c r="AH23" t="n">
-        <v>28.71</v>
+        <v>28.81</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -10535,13 +11015,13 @@
         <v>0.001</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.038179</v>
+        <v>0.039881</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.079039</v>
+        <v>1.083631</v>
       </c>
       <c r="AM23" t="n">
-        <v>7.9</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -10571,10 +11051,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.037934</v>
+        <v>0.037688</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.0065</v>
+        <v>1.0582</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -10726,10 +11206,10 @@
         <v>0</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.5395</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.2698</v>
+        <v>0.273</v>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
@@ -10815,13 +11295,13 @@
         <v>1.0091</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0457</v>
+        <v>0.0335</v>
       </c>
       <c r="Q24" t="n">
         <v>459</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4557</v>
+        <v>0.4527</v>
       </c>
       <c r="S24" t="n">
         <v>285</v>
@@ -10865,13 +11345,13 @@
         <v>0.1632</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0174</v>
+        <v>0.016</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.5794</v>
+        <v>0.5102</v>
       </c>
       <c r="AH24" t="n">
-        <v>21.88</v>
+        <v>22.22</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -10880,13 +11360,13 @@
         <v>0.1758</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.047635</v>
+        <v>0.064485</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.922635</v>
+        <v>0.939069</v>
       </c>
       <c r="AM24" t="n">
-        <v>-7.74</v>
+        <v>-6.09</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -10916,10 +11396,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.048438</v>
+        <v>0.044604</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.9834000000000001</v>
+        <v>1.4457</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -11071,7 +11551,7 @@
         <v>1</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.4781</v>
+        <v>0.5382</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -11126,7 +11606,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -11202,13 +11682,13 @@
         <v>0.0936</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0843</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.8949</v>
+        <v>0.9044</v>
       </c>
       <c r="AH25" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -11217,13 +11697,13 @@
         <v>0.0467</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.198589</v>
+        <v>-0.1891</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.505651</v>
+        <v>0.502288</v>
       </c>
       <c r="AM25" t="n">
-        <v>-49.43</v>
+        <v>-49.77</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -11253,10 +11733,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.235304</v>
+        <v>0.237123</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.844</v>
+        <v>0.7975</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -11266,7 +11746,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -11408,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.3971</v>
+        <v>0.3905</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -11451,7 +11931,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -11539,13 +12019,13 @@
         <v>-0.0785</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0267</v>
+        <v>0.0263</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="AH26" t="n">
-        <v>10.76</v>
+        <v>10.87</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -11554,13 +12034,13 @@
         <v>-0.0037</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.000244</v>
+        <v>0.006966</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.032815</v>
+        <v>1.038538</v>
       </c>
       <c r="AM26" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -11590,10 +12070,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.074591</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.0033</v>
+        <v>0.0949</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -11741,7 +12221,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3464</v>
+        <v>0.3588</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -11887,13 +12367,13 @@
         <v>0.0274</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.028489</v>
+        <v>0.027088</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.5408539999999999</v>
+        <v>0.542214</v>
       </c>
       <c r="AM27" t="n">
-        <v>-45.91</v>
+        <v>-45.78</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -11926,7 +12406,7 @@
         <v>0.103046</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.2765</v>
+        <v>0.2629</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -12074,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.3112</v>
+        <v>0.3098</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -12205,13 +12685,13 @@
         <v>0.1294</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0267</v>
+        <v>0.0269</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.6091</v>
+        <v>0.6173</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -12220,13 +12700,13 @@
         <v>0.0809</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.015322</v>
+        <v>0.011113</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.868484</v>
+        <v>0.864243</v>
       </c>
       <c r="AM28" t="n">
-        <v>-13.15</v>
+        <v>-13.58</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -12256,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.074547</v>
+        <v>0.075196</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.2055</v>
+        <v>0.1478</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -12411,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.4109</v>
+        <v>0.4035</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -12449,7 +12929,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12458,15 +12938,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -12479,7 +12963,7 @@
         <v>0.7328</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3037</v>
+        <v>0.3015</v>
       </c>
       <c r="N29" t="n">
         <v>0.9288999999999999</v>
@@ -12503,7 +12987,7 @@
         <v>0.1613</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0548</v>
+        <v>0.0546</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -12542,28 +13026,28 @@
         <v>0.056</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.013</v>
+        <v>0.0131</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.1951</v>
+        <v>0.1987</v>
       </c>
       <c r="AH29" t="n">
-        <v>14.53</v>
+        <v>14.68</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>15.13</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.0441</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.024142</v>
+        <v>0.030556</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.187845</v>
+        <v>1.19085</v>
       </c>
       <c r="AM29" t="n">
-        <v>18.78</v>
+        <v>19.08</v>
       </c>
       <c r="AN29" t="n">
         <v>1</v>
@@ -12590,13 +13074,13 @@
         <v>1</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.03635</v>
+        <v>0.036522</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.6642</v>
+        <v>0.8366</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -12606,7 +13090,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -12744,27 +13228,71 @@
         <v>1</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4709</v>
+        <v>0.4874</v>
       </c>
       <c r="CQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR29" t="inlineStr"/>
-      <c r="CS29" t="inlineStr"/>
-      <c r="CT29" t="inlineStr"/>
-      <c r="CU29" t="inlineStr"/>
-      <c r="CV29" t="inlineStr"/>
-      <c r="CW29" t="inlineStr"/>
+        <v>0.4874</v>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>Bull spread largo: compra call delta~45, venda call delta~15</t>
+        </is>
+      </c>
+      <c r="CS29" t="inlineStr">
+        <is>
+          <t>Call naked delta~45 (se rv_rank &lt; 0.60)</t>
+        </is>
+      </c>
+      <c r="CT29" t="inlineStr">
+        <is>
+          <t>Bull spread estreito: compra delta~45, venda delta~25</t>
+        </is>
+      </c>
+      <c r="CU29" t="inlineStr">
+        <is>
+          <t>Spread ainda mais largo que 45/15; ratio spread</t>
+        </is>
+      </c>
+      <c r="CV29" t="inlineStr">
+        <is>
+          <t>~0.45 (perna longa)</t>
+        </is>
+      </c>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>naked_30: esp=+0.160 | naked_45: esp=+0.193 | spread_35_20: esp=+0.023 | spread_45_25: esp=+0.024</t>
+        </is>
+      </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>Ticker neutro — sem sinal operacional</t>
-        </is>
-      </c>
-      <c r="CY29" t="inlineStr"/>
-      <c r="CZ29" t="inlineStr"/>
-      <c r="DA29" t="inlineStr"/>
-      <c r="DB29" t="inlineStr"/>
-      <c r="DC29" t="inlineStr"/>
+          <t>[Empírico] Bull spread largo: compra call delta~45, venda call delta~15 — esp_estrutura=0.056 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco (vol via HAR — naked vetado por risco).</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>OBRIGATÓRIO: débito ≤ 50% da largura entre strikes (ideal ≤ 33% para relação lucro/perda 2:1). Se débito &gt; 50%: aproximar strikes ou aguardar. rv_rank=0.20 — custo aceitável. [Carry 20 pregões: 1.05% — preferir spread bull/bear sobre naked para calls em carry alto]</t>
+        </is>
+      </c>
+      <c r="DA29" t="inlineStr">
+        <is>
+          <t>50% do lucro máximo da trava</t>
+        </is>
+      </c>
+      <c r="DB29" t="inlineStr">
+        <is>
+          <t>100% do débito pago</t>
+        </is>
+      </c>
+      <c r="DC29" t="inlineStr">
+        <is>
+          <t>Trava limita upside — sair em 50% do max. Stop = débito total.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12822,7 +13350,7 @@
         <v>0.4201</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.1615</v>
+        <v>-0.1629</v>
       </c>
       <c r="P30" t="n">
         <v>-0.0142</v>
@@ -12837,7 +13365,7 @@
         <v>322</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.0311</v>
+        <v>-0.0313</v>
       </c>
       <c r="U30" t="n">
         <v>0.0343</v>
@@ -12864,43 +13392,43 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.0321</v>
+        <v>-0.0323</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.008</v>
+        <v>0.0072</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.0045</v>
+        <v>0.0037</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0245</v>
+        <v>0.0236</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.028</v>
+        <v>0.0271</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0117</v>
+        <v>0.0116</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.2698</v>
+        <v>0.2672</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.92</v>
+        <v>18.87</v>
       </c>
       <c r="AI30" t="n">
-        <v>19.43</v>
+        <v>19.38</v>
       </c>
       <c r="AJ30" t="n">
         <v>-0.0046</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.055746</v>
+        <v>0.054957</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.121181</v>
+        <v>1.122789</v>
       </c>
       <c r="AM30" t="n">
-        <v>12.12</v>
+        <v>12.28</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -12930,10 +13458,10 @@
         <v>1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.032563</v>
+        <v>0.032463</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.7119</v>
+        <v>1.6929</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -13081,10 +13609,10 @@
         <v>0</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5799</v>
+        <v>0.5785</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.5799</v>
+        <v>0.5785</v>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
@@ -13224,13 +13752,13 @@
         <v>-0.2521</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0142</v>
+        <v>0.0143</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.2694</v>
+        <v>0.2758</v>
       </c>
       <c r="AH31" t="n">
-        <v>26.15</v>
+        <v>26.41</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -13239,13 +13767,13 @@
         <v>-0.0056</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.016579</v>
+        <v>0.020721</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.052269</v>
+        <v>1.044831</v>
       </c>
       <c r="AM31" t="n">
-        <v>5.23</v>
+        <v>4.48</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -13275,10 +13803,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.039595</v>
+        <v>0.039965</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.4187</v>
+        <v>0.5185</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -13426,7 +13954,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.4701</v>
+        <v>0.4788</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -13553,13 +14081,13 @@
         <v>-0.0619</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0187</v>
+        <v>0.019</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.3663</v>
+        <v>0.3781</v>
       </c>
       <c r="AH32" t="n">
-        <v>33.3</v>
+        <v>33.63</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -13568,13 +14096,13 @@
         <v>0.0147</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.008548</v>
+        <v>0.011423</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.7759470000000001</v>
+        <v>0.778331</v>
       </c>
       <c r="AM32" t="n">
-        <v>-22.41</v>
+        <v>-22.17</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
@@ -13604,10 +14132,10 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.052264</v>
+        <v>0.052923</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.1636</v>
+        <v>0.2158</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -13755,7 +14283,7 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.404</v>
+        <v>0.4069</v>
       </c>
       <c r="CQ32" t="n">
         <v>0</v>
@@ -13832,13 +14360,13 @@
         <v>-0.0968</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.0347</v>
+        <v>-0.0367</v>
       </c>
       <c r="Q33" t="n">
         <v>459</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.0312</v>
+        <v>-0.033</v>
       </c>
       <c r="S33" t="n">
         <v>402</v>
@@ -13886,13 +14414,13 @@
         <v>-0.08550000000000001</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.018</v>
+        <v>0.0181</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2227</v>
+        <v>0.2243</v>
       </c>
       <c r="AH33" t="n">
-        <v>21.18</v>
+        <v>21.36</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -13901,13 +14429,13 @@
         <v>0.0023</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.015753</v>
+        <v>0.018409</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.959952</v>
+        <v>0.954458</v>
       </c>
       <c r="AM33" t="n">
-        <v>-4</v>
+        <v>-4.55</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -13937,10 +14465,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.05031</v>
+        <v>0.050408</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.3131</v>
+        <v>0.3652</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -14092,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4646</v>
+        <v>0.4695</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -14223,13 +14751,13 @@
         <v>-0.0747</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0147</v>
+        <v>0.0146</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.3292</v>
+        <v>0.3229</v>
       </c>
       <c r="AH34" t="n">
-        <v>27.23</v>
+        <v>27.38</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -14238,13 +14766,13 @@
         <v>0.0015</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.024821</v>
+        <v>0.02757</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.976729</v>
+        <v>0.973114</v>
       </c>
       <c r="AM34" t="n">
-        <v>-2.33</v>
+        <v>-2.69</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -14274,10 +14802,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.041107</v>
+        <v>0.040743</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.6038</v>
+        <v>0.6767</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -14429,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.4367</v>
+        <v>0.4453</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -14556,13 +15084,13 @@
         <v>0.1567</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0186</v>
+        <v>0.0182</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.2469</v>
+        <v>0.2358</v>
       </c>
       <c r="AH35" t="n">
-        <v>54.21</v>
+        <v>54.73</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -14571,13 +15099,13 @@
         <v>0.0109</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.06184</v>
+        <v>-0.059353</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.899316</v>
+        <v>0.8996960000000001</v>
       </c>
       <c r="AM35" t="n">
-        <v>-10.07</v>
+        <v>-10.03</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -14607,10 +15135,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.051993</v>
+        <v>0.050841</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.1894</v>
+        <v>1.1674</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -14892,10 +15420,10 @@
         <v>0.0403</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.6925</v>
+        <v>0.6934</v>
       </c>
       <c r="AH36" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -14904,13 +15432,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.112478</v>
+        <v>0.108039</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.988289</v>
+        <v>0.987726</v>
       </c>
       <c r="AM36" t="n">
-        <v>-1.17</v>
+        <v>-1.23</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -14940,10 +15468,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.112467</v>
+        <v>0.11254</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.0001</v>
+        <v>0.96</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -15091,7 +15619,7 @@
         <v>1</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.4511</v>
+        <v>0.4469</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -15218,13 +15746,13 @@
         <v>-0.0021</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0135</v>
+        <v>0.0134</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.3155</v>
+        <v>0.3083</v>
       </c>
       <c r="AH37" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -15233,13 +15761,13 @@
         <v>0.0119</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.00665</v>
+        <v>0.008874999999999999</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.876444</v>
+        <v>0.870272</v>
       </c>
       <c r="AM37" t="n">
-        <v>-12.36</v>
+        <v>-12.97</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -15269,10 +15797,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.037743</v>
+        <v>0.037342</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.1762</v>
+        <v>0.2377</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -15420,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.435</v>
+        <v>0.4426</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -15547,13 +16075,13 @@
         <v>-0.0549</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0279</v>
+        <v>0.028</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.5412</v>
+        <v>0.5431</v>
       </c>
       <c r="AH38" t="n">
-        <v>34.45</v>
+        <v>34.41</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -15562,13 +16090,13 @@
         <v>0.0146</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.06412</v>
+        <v>0.06308900000000001</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.942049</v>
+        <v>0.941286</v>
       </c>
       <c r="AM38" t="n">
-        <v>-5.8</v>
+        <v>-5.87</v>
       </c>
       <c r="AN38" t="n">
         <v>0</v>
@@ -15598,10 +16126,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.07788299999999999</v>
+        <v>0.07804999999999999</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.8233</v>
+        <v>0.8083</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -15753,7 +16281,7 @@
         <v>0</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.4446</v>
+        <v>0.4428</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -15884,13 +16412,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0209</v>
+        <v>0.0207</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.6484</v>
+        <v>0.6307</v>
       </c>
       <c r="AH39" t="n">
-        <v>14.95</v>
+        <v>15.06</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -15899,13 +16427,13 @@
         <v>-0.0011</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.035318</v>
+        <v>0.03778</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.86557</v>
+        <v>0.8619</v>
       </c>
       <c r="AM39" t="n">
-        <v>-13.44</v>
+        <v>-13.81</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -15935,10 +16463,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.058408</v>
+        <v>0.057663</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.6047</v>
+        <v>0.6552</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -16090,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.4506</v>
+        <v>0.4592</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -16217,13 +16745,13 @@
         <v>-0.0004</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0157</v>
+        <v>0.016</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.4205</v>
+        <v>0.4387</v>
       </c>
       <c r="AH40" t="n">
-        <v>48.61</v>
+        <v>48.87</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -16232,13 +16760,13 @@
         <v>0.0367</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.016525</v>
+        <v>-0.014703</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.073749</v>
+        <v>1.064362</v>
       </c>
       <c r="AM40" t="n">
-        <v>7.37</v>
+        <v>6.44</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -16268,10 +16796,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.04393</v>
+        <v>0.044706</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.3762</v>
+        <v>0.3289</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -16423,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.4308</v>
+        <v>0.4225</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -16494,7 +17022,7 @@
         <v>0.6044</v>
       </c>
       <c r="N41" t="n">
-        <v>1.3214</v>
+        <v>1.3241</v>
       </c>
       <c r="O41" t="n">
         <v>0.9082</v>
@@ -16512,10 +17040,10 @@
         <v>401</v>
       </c>
       <c r="T41" t="n">
-        <v>0.845</v>
+        <v>0.8469</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0987</v>
+        <v>0.099</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -16539,10 +17067,10 @@
         <v>1.535</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.844</v>
+        <v>0.8459</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.0343</v>
+        <v>1.0361</v>
       </c>
       <c r="AC41" t="n">
         <v>0.2054</v>
@@ -16554,28 +17082,28 @@
         <v>0.3917</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.1072</v>
+        <v>0.0954</v>
       </c>
       <c r="AG41" t="n">
-        <v>1</v>
+        <v>0.9394</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.1411</v>
+        <v>0.1414</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.277978</v>
+        <v>-0.31704</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.750288</v>
+        <v>0.815859</v>
       </c>
       <c r="AM41" t="n">
-        <v>-24.97</v>
+        <v>-18.41</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -16587,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
         <v>1.039087</v>
@@ -16605,10 +17133,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.29929</v>
+        <v>0.266327</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.9288</v>
+        <v>1.1904</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -16756,7 +17284,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.3808</v>
+        <v>0.4191</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -16886,10 +17414,10 @@
         <v>0.018</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4277</v>
+        <v>0.4263</v>
       </c>
       <c r="AH42" t="n">
-        <v>18.75</v>
+        <v>18.87</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -16898,13 +17426,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.052147</v>
+        <v>0.055145</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.948499</v>
+        <v>0.948742</v>
       </c>
       <c r="AM42" t="n">
-        <v>-5.15</v>
+        <v>-5.13</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -16934,10 +17462,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.050316</v>
+        <v>0.050237</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.0364</v>
+        <v>1.0977</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -17089,7 +17617,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.5278</v>
+        <v>0.5342</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -17549,13 +18077,13 @@
         <v>0.2183</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.031</v>
+        <v>0.0305</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.6538</v>
+        <v>0.6378</v>
       </c>
       <c r="AH44" t="n">
-        <v>6.84</v>
+        <v>6.91</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -17564,13 +18092,13 @@
         <v>0.113</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.031029</v>
+        <v>0.036567</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.758026</v>
+        <v>0.753378</v>
       </c>
       <c r="AM44" t="n">
-        <v>-24.2</v>
+        <v>-24.66</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -17600,10 +18128,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.08643099999999999</v>
+        <v>0.085109</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.359</v>
+        <v>0.4297</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -17755,7 +18283,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.3717</v>
+        <v>0.382</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -17889,10 +18417,10 @@
         <v>0.0144</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.3827</v>
+        <v>0.3852</v>
       </c>
       <c r="AH45" t="n">
-        <v>29.59</v>
+        <v>29.61</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -17901,13 +18429,13 @@
         <v>-0.0116</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.031626</v>
+        <v>-0.031585</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.101418</v>
+        <v>1.099509</v>
       </c>
       <c r="AM45" t="n">
-        <v>10.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -17937,10 +18465,10 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.040095</v>
+        <v>0.040211</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.7855</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -18092,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.4871</v>
+        <v>0.4863</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -18223,13 +18751,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0297</v>
+        <v>0.0296</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.6793</v>
+        <v>0.6765</v>
       </c>
       <c r="AH46" t="n">
-        <v>14.35</v>
+        <v>14.4</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -18238,13 +18766,13 @@
         <v>-0.0015</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.089305</v>
+        <v>0.08970499999999999</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.973264</v>
+        <v>0.971795</v>
       </c>
       <c r="AM46" t="n">
-        <v>-2.67</v>
+        <v>-2.82</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -18274,10 +18802,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.082866</v>
+        <v>0.082662</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.0777</v>
+        <v>1.0852</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -18425,7 +18953,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.439</v>
+        <v>0.4404</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -37289,7 +37817,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -37361,7 +37889,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -37685,7 +38213,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -37829,12 +38357,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -38679,7 +39207,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.4749</v>
+        <v>0.4735</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -38837,7 +39365,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5936</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -38949,7 +39477,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.3767</v>
+        <v>0.3752</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -39219,7 +39747,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4744</v>
+        <v>0.4702</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -39285,7 +39813,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.319</v>
+        <v>0.333</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -39443,7 +39971,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.4174</v>
+        <v>0.4179</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -39509,7 +40037,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.5334</v>
+        <v>0.5218</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -39667,7 +40195,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.325</v>
+        <v>0.3284</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -39779,7 +40307,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4765</v>
+        <v>0.4701</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -40041,15 +40569,15 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.444</v>
+        <v>0.4497</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -40157,7 +40685,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.5092</v>
+        <v>0.4976</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -40219,15 +40747,15 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.4293</v>
+        <v>0.4699</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -40289,7 +40817,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0.4326</v>
+        <v>0.4329</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -40401,7 +40929,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.5139</v>
+        <v>0.5131</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -40513,7 +41041,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4645</v>
+        <v>0.4643</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -40579,7 +41107,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.3665</v>
+        <v>0.3688</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -40691,7 +41219,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.3586</v>
+        <v>0.3582</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -40757,7 +41285,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.3636</v>
+        <v>0.3579</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -41007,7 +41535,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.5395</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -41073,7 +41601,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.4781</v>
+        <v>0.5382</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -41135,15 +41663,15 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.3971</v>
+        <v>0.3905</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -41205,7 +41733,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.3464</v>
+        <v>0.3588</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -41409,7 +41937,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.3112</v>
+        <v>0.3098</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -41475,7 +42003,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.4109</v>
+        <v>0.4035</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -41532,20 +42060,20 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Neutro</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.4709</v>
+        <v>0.4874</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -41607,7 +42135,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5799</v>
+        <v>0.5785</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -41673,7 +42201,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4701</v>
+        <v>0.4788</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -41969,7 +42497,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.404</v>
+        <v>0.4069</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -42357,7 +42885,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.4646</v>
+        <v>0.4695</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -42469,7 +42997,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.4367</v>
+        <v>0.4453</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -42643,7 +43171,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.4511</v>
+        <v>0.4469</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -42797,7 +43325,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.435</v>
+        <v>0.4426</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -42863,7 +43391,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.4446</v>
+        <v>0.4428</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -42929,7 +43457,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.4506</v>
+        <v>0.4592</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -42995,7 +43523,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4308</v>
+        <v>0.4225</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -43325,7 +43853,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.3808</v>
+        <v>0.4191</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -43525,7 +44053,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5278</v>
+        <v>0.5342</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -43749,7 +44277,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3717</v>
+        <v>0.382</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -43861,7 +44389,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.4871</v>
+        <v>0.4863</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -43927,7 +44455,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.439</v>
+        <v>0.4404</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -44245,7 +44773,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -44255,7 +44783,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -44275,7 +44803,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -44305,7 +44833,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -44345,7 +44873,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
